--- a/manual-qa-repository/07-execution/TestCases-Consolidated.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-Consolidated.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15238" uniqueCount="4703">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16678" uniqueCount="5248">
   <si>
     <t>TC ID</t>
   </si>
@@ -14778,6 +14778,1641 @@
   </si>
   <si>
     <t>`[VISUAL_GAP — unauthenticated state not captured]` — derived from INDEX.md note; recommend Tech Lead capture a redirected-state screenshot before automation</t>
+  </si>
+  <si>
+    <t>TC_CBR_UI_001</t>
+  </si>
+  <si>
+    <t>Page loads with greeting + 8 summary cards + table</t>
+  </si>
+  <si>
+    <t>SM logged in; session at `automation-repository/fixtures/.auth/sales-manager.json`</t>
+  </si>
+  <si>
+    <t>1. Navigate to `/sales-manager/callback-requests`. 2. Wait for `networkidle`. 3. Inspect top region for `h5:has-text("Welcome")` and summary card heading strip. 4. Inspect main region for the requests table.</t>
+  </si>
+  <si>
+    <t>Heading "Welcome, Tester" rendered. 8 summary cards visible in horizontal strip with `h5` headings: Total SM, Total VC Request, Total VC Pending, Invite Sent/Re-sent, Meeting Done, SM Feedback Done, Customer Feedback Done, Avg Rating by Customer. Each card shows a numeric value. Requests table rendered below with column headers visible.</t>
+  </si>
+  <si>
+    <t>SM-FS-CBR §1.6 KPI Cards</t>
+  </si>
+  <si>
+    <t>`callback-loaded.png`</t>
+  </si>
+  <si>
+    <t>TC_CBR_UI_002</t>
+  </si>
+  <si>
+    <t>Summary card "Total VC Request" shows SM / Buyer fraction</t>
+  </si>
+  <si>
+    <t>Page loaded per TC_CBR_UI_001</t>
+  </si>
+  <si>
+    <t>1. Locate card titled "Total VC Request". 2. Read its value text.</t>
+  </si>
+  <si>
+    <t>Value displayed as a fraction "X / Y" (e.g., "40 / 34") — SM-perceived count over Buyer-perceived count. Not a single integer.</t>
+  </si>
+  <si>
+    <t>SM-FS-CBR §1.6</t>
+  </si>
+  <si>
+    <t>TC_CBR_UI_003</t>
+  </si>
+  <si>
+    <t>Sidebar shows Callback Requests as selected nav item</t>
+  </si>
+  <si>
+    <t>1. Open `/sales-manager/callback-requests`. 2. Inspect left sidebar.</t>
+  </si>
+  <si>
+    <t>Sidebar contains 3 nav icons: Callback Requests (selected, with `.ant-menu-item-selected` class), Towers, Allocation; plus Logout link at bottom. Callback Requests is the default landing route after OTP login per `routes/Private/sales-manager/index.jsx` `&lt;Route index element={&lt;Navigate to="callback-requests" replace /&gt;}&gt;`.</t>
+  </si>
+  <si>
+    <t>SM-FS-CBR §1.2</t>
+  </si>
+  <si>
+    <t>TC_CBR_UI_004</t>
+  </si>
+  <si>
+    <t>Top banner displays growth-housing announcement</t>
+  </si>
+  <si>
+    <t>Page loaded</t>
+  </si>
+  <si>
+    <t>1. Inspect top banner region above main content.</t>
+  </si>
+  <si>
+    <t>Banner text reads "India's Biggest Growth Housing Revolution Begins On 7th April 2026."</t>
+  </si>
+  <si>
+    <t>TC_CBR_UI_005</t>
+  </si>
+  <si>
+    <t>Table renders all 16 columns</t>
+  </si>
+  <si>
+    <t>Page loaded with at least one row</t>
+  </si>
+  <si>
+    <t>1. Inspect `thead` of the requests table. 2. Enumerate column headers left to right.</t>
+  </si>
+  <si>
+    <t>16 column headers in order: (1) bulk-select checkbox, (2) Request ID (sortable), (3) Manager, (4) Customer Name, (5) Customer Phone, (6) Registration No, (7) HV Code, (8) Pincode, (9) Requested At (sortable), (10) Status (with filter trigger), (11) VC Outcome (with filter trigger), (12) Meeting, (13) SM Feedback, (14) Customer Rating, (15) Customer Email, (16) Actions.</t>
+  </si>
+  <si>
+    <t>SM-FS-CBR §1.4</t>
+  </si>
+  <si>
+    <t>`callback-table-data.png`</t>
+  </si>
+  <si>
+    <t>TC_CBR_UI_006</t>
+  </si>
+  <si>
+    <t>Status badges render with correct colour classes</t>
+  </si>
+  <si>
+    <t>Table has at least one PENDING and one MEETING DONE row</t>
+  </si>
+  <si>
+    <t>1. Locate Status column cells. 2. Inspect each `&lt;span class="ant-tag …"&gt;` for class and text.</t>
+  </si>
+  <si>
+    <t>PENDING rows → `ant-tag ant-tag-yellow` containing text "PENDING". MEETING DONE rows → `ant-tag ant-tag-green` containing text "MEETING DONE" or "CONFIRMED". Colour classes match badge text.</t>
+  </si>
+  <si>
+    <t>SM-FS-CBR §1.5</t>
+  </si>
+  <si>
+    <t>TC_CBR_UI_007</t>
+  </si>
+  <si>
+    <t>Actions column shows exactly 2 row icons</t>
+  </si>
+  <si>
+    <t>Any row visible</t>
+  </si>
+  <si>
+    <t>1. Inspect the last cell of any data row.</t>
+  </si>
+  <si>
+    <t>Two `anticon` icons side-by-side: (1) `.anticon-eye` green colour `rgb(80, 185, 95)` size 18px; (2) `.anticon-more` (3 vertical dots) gray colour. No other action icons.</t>
+  </si>
+  <si>
+    <t>SM-FS-CBR §1.4 (Actions surface)</t>
+  </si>
+  <si>
+    <t>TC_CBR_FUNC_008</t>
+  </si>
+  <si>
+    <t>"Select Sales Manager" filter dropdown lists 10 manager options</t>
+  </si>
+  <si>
+    <t>Page loaded as SM Admin (sees all managers)</t>
+  </si>
+  <si>
+    <t>1. Click the "Select Sales Manager" Ant Select trigger above the table.</t>
+  </si>
+  <si>
+    <t>Dropdown opens. 10 manager names rendered as selectable options.</t>
+  </si>
+  <si>
+    <t>SM-FS-CBR §1.7 BR2 (SM Admin reassign)</t>
+  </si>
+  <si>
+    <t>`callback-filter-open.png`</t>
+  </si>
+  <si>
+    <t>TC_CBR_FUNC_009</t>
+  </si>
+  <si>
+    <t>Status column header filter exposes 4 status checkboxes</t>
+  </si>
+  <si>
+    <t>1. Click the filter trigger in the Status column header (`th:has-text("Status") .ant-table-filter-trigger`).</t>
+  </si>
+  <si>
+    <t>Filter dropdown opens with exactly 4 checkbox options: Pending, Resent Invite, Sent Invite, Meeting Done. Each is a separate `.ant-checkbox-wrapper`.</t>
+  </si>
+  <si>
+    <t>`callback-status-filter.png`</t>
+  </si>
+  <si>
+    <t>TC_CBR_FUNC_010</t>
+  </si>
+  <si>
+    <t>Status filter checkbox selection filters the table</t>
+  </si>
+  <si>
+    <t>Multiple status values present in table</t>
+  </si>
+  <si>
+    <t>1. Open Status filter (TC_CBR_FUNC_009). 2. Check only "Pending". 3. Apply / click outside.</t>
+  </si>
+  <si>
+    <t>Only PENDING rows remain visible. Other status rows hidden. Total counter reflects filtered count.</t>
+  </si>
+  <si>
+    <t>TC_CBR_FUNC_011</t>
+  </si>
+  <si>
+    <t>VC Outcome column has a filter trigger</t>
+  </si>
+  <si>
+    <t>1. Inspect VC Outcome column header for `.ant-table-filter-trigger`.</t>
+  </si>
+  <si>
+    <t>Filter trigger element exists in VC Outcome column header (filter UI for outcome codes).</t>
+  </si>
+  <si>
+    <t>SM-FS-CBR §4.3 (10 outcome codes)</t>
+  </si>
+  <si>
+    <t>TC_CBR_FUNC_012</t>
+  </si>
+  <si>
+    <t>Date range pickers accept Start Date and End Date</t>
+  </si>
+  <si>
+    <t>1. Locate `input[placeholder="Start Date"]` and `input[placeholder="End Date"]`. 2. Pick a start date and end date that span the data.</t>
+  </si>
+  <si>
+    <t>Both Ant DatePicker inputs accept values. Table reloads showing only rows whose Requested At falls within the range.</t>
+  </si>
+  <si>
+    <t>SM-FS-CBR §1.4 (Requested Date/Time column)</t>
+  </si>
+  <si>
+    <t>TC_CBR_FUNC_013</t>
+  </si>
+  <si>
+    <t>Search box filters table by name / phone / email / reg no</t>
+  </si>
+  <si>
+    <t>Page loaded with rows</t>
+  </si>
+  <si>
+    <t>1. In `input[placeholder="Search by name, phone, email, reg no..."]`, type a known customer name. 2. Submit / wait debounce.</t>
+  </si>
+  <si>
+    <t>Table updates to show only matching rows. Counter updates.</t>
+  </si>
+  <si>
+    <t>TC_CBR_FUNC_014</t>
+  </si>
+  <si>
+    <t>Search yielding no match displays empty state</t>
+  </si>
+  <si>
+    <t>1. In search box, type `ZZZZZNOMATCH123XYZ`. 2. Wait.</t>
+  </si>
+  <si>
+    <t>Table shows Ant empty illustration with description text "No data". Counter reads "Total 0 Callback Requests".</t>
+  </si>
+  <si>
+    <t>`callback-empty-state.png`</t>
+  </si>
+  <si>
+    <t>TC_CBR_FUNC_015</t>
+  </si>
+  <si>
+    <t>Pagination "10 / page" selector at table footer</t>
+  </si>
+  <si>
+    <t>Page loaded with &gt; 10 rows</t>
+  </si>
+  <si>
+    <t>1. Scroll to bottom-right of table. 2. Inspect page-size selector.</t>
+  </si>
+  <si>
+    <t>Page-size selector reads "10 / page" by default. Page navigator visible.</t>
+  </si>
+  <si>
+    <t>TC_CBR_FUNC_016</t>
+  </si>
+  <si>
+    <t>Refresh button reloads table</t>
+  </si>
+  <si>
+    <t>1. Click `button:has-text("Refresh")`.</t>
+  </si>
+  <si>
+    <t>Table data re-fetches and re-renders. Active filters / search preserved.</t>
+  </si>
+  <si>
+    <t>SM-FS-CBR §1.4 (table refresh)</t>
+  </si>
+  <si>
+    <t>TC_CBR_FUNC_017</t>
+  </si>
+  <si>
+    <t>Export button is present in toolbar</t>
+  </si>
+  <si>
+    <t>1. Inspect toolbar for `button:has-text("Export")`.</t>
+  </si>
+  <si>
+    <t>Export button rendered and clickable.</t>
+  </si>
+  <si>
+    <t>SM-FS-CBR §1.8 (audit / logging surfaces)</t>
+  </si>
+  <si>
+    <t>TC_CBR_FUNC_018</t>
+  </si>
+  <si>
+    <t>Bulk-assign "Assign (0)" button reflects selected count</t>
+  </si>
+  <si>
+    <t>Page loaded; no rows selected</t>
+  </si>
+  <si>
+    <t>1. Inspect bulk-action button text. 2. Tick a row checkbox.</t>
+  </si>
+  <si>
+    <t>Initially button text reads "Assign (0)" (disabled). After selecting 1 row, text updates to "Assign (1)".</t>
+  </si>
+  <si>
+    <t>SM-FS-CBR §1.7 BR2 (reassignment)</t>
+  </si>
+  <si>
+    <t>TC_CBR_FUNC_019</t>
+  </si>
+  <si>
+    <t>Eye icon opens Callback Request Details drawer with 3 tabs</t>
+  </si>
+  <si>
+    <t>At least one row in table</t>
+  </si>
+  <si>
+    <t>1. Click `.anticon-eye` in any row.</t>
+  </si>
+  <si>
+    <t>Right-side drawer opens with title "Callback Request Details". 3 Ant Tabs visible: "Callback Request" (active by default), "Feedback", "Callback History".</t>
+  </si>
+  <si>
+    <t>SM-FS-CBR §1.4 (detail drawer)</t>
+  </si>
+  <si>
+    <t>`callback-details-drawer-pending.png`</t>
+  </si>
+  <si>
+    <t>TC_CBR_FUNC_020</t>
+  </si>
+  <si>
+    <t>Details drawer "Callback Request" tab is READ-ONLY for PENDING row</t>
+  </si>
+  <si>
+    <t>PENDING row exists</t>
+  </si>
+  <si>
+    <t>1. Click eye icon on PENDING row REQ-00075. 2. Inspect drawer body. 3. Attempt to edit any field.</t>
+  </si>
+  <si>
+    <t>Drawer renders sections: Customer Information, Registration Preferences, Description, Customer Units table. No editable fields exist. Only the `.ant-drawer-close` button is interactive.</t>
+  </si>
+  <si>
+    <t>SM-FS-CBR §1.7 BR3 (immutability of detail view)</t>
+  </si>
+  <si>
+    <t>TC_CBR_FUNC_021</t>
+  </si>
+  <si>
+    <t>Details drawer "Callback Request" tab on MEETING DONE row shows CONFIRMED status</t>
+  </si>
+  <si>
+    <t>MEETING DONE row exists</t>
+  </si>
+  <si>
+    <t>1. Click eye icon on MEETING DONE row REQ-00073.</t>
+  </si>
+  <si>
+    <t>Drawer opens with same section layout; Status field reads "CONFIRMED" (per FSD-CORRECTION fallback from COMPLETED).</t>
+  </si>
+  <si>
+    <t>SM-FS-CBR §1.5 + FSD-CORRECTION 2026-05-25</t>
+  </si>
+  <si>
+    <t>`callback-details-drawer-meetingdone.png`</t>
+  </si>
+  <si>
+    <t>TC_CBR_FUNC_022</t>
+  </si>
+  <si>
+    <t>Details drawer "Feedback" tab shows all SM Feedback fields</t>
+  </si>
+  <si>
+    <t>Eye-icon drawer open on MEETING DONE row</t>
+  </si>
+  <si>
+    <t>1. Click `.ant-drawer-open .ant-tabs-tab:has-text("Feedback")`. 2. Inspect rendered fields.</t>
+  </si>
+  <si>
+    <t>Tab activates. "Sales Manager Feedback" section renders fields: Submitted at, Intent, Allocation Day Confirmation, Typology, Budget, Floor Preference (Min-Max), Lost Reason, Home Loan, Parking Required, Remark, Next Step. Below it, "Registration Preferences" sub-section listing TOWER/UNIT picks (e.g., Tower 8 - Crest unit 1301).</t>
+  </si>
+  <si>
+    <t>SM-FS-CBR §4 (Record VC Outcome → feedback)</t>
+  </si>
+  <si>
+    <t>`callback-details-feedback-tab.png`</t>
+  </si>
+  <si>
+    <t>TC_CBR_FUNC_023</t>
+  </si>
+  <si>
+    <t>Details drawer "Callback History" tab shows history table</t>
+  </si>
+  <si>
+    <t>Eye-icon drawer open</t>
+  </si>
+  <si>
+    <t>1. Click `.ant-drawer-open .ant-tabs-tab:has-text("Callback History")`.</t>
+  </si>
+  <si>
+    <t>Tab activates. Section heading "Callback History for GHNG-…" rendered. Table columns: Request ID, Requested At, Manager Name, VC Outcome, Status, View.</t>
+  </si>
+  <si>
+    <t>SM-WF-CBR §6 BR7 (rescheduling preserves history)</t>
+  </si>
+  <si>
+    <t>`callback-details-history-tab.png`</t>
+  </si>
+  <si>
+    <t>TC_CBR_FUNC_024</t>
+  </si>
+  <si>
+    <t>Details drawer close button dismisses drawer</t>
+  </si>
+  <si>
+    <t>1. Click `.ant-drawer-open .ant-drawer-close`.</t>
+  </si>
+  <si>
+    <t>Drawer closes; underlying table regains focus.</t>
+  </si>
+  <si>
+    <t>TC_CBR_FUNC_025</t>
+  </si>
+  <si>
+    <t>More icon opens dropdown with single "Capture VC Outcome" item — PENDING row</t>
+  </si>
+  <si>
+    <t>1. Click `.anticon-more` in PENDING row.</t>
+  </si>
+  <si>
+    <t>Ant Dropdown opens. Exactly ONE menu item: "Capture VC Outcome". No "Schedule Meeting", no "Confirm Meeting", no "Reschedule" — single action only.</t>
+  </si>
+  <si>
+    <t>SM-FS-CBR §4.1 + Arch. Correction</t>
+  </si>
+  <si>
+    <t>`callback-row-more-menu.png`</t>
+  </si>
+  <si>
+    <t>TC_CBR_FUNC_026</t>
+  </si>
+  <si>
+    <t>More icon opens same single-item dropdown on MEETING DONE row</t>
+  </si>
+  <si>
+    <t>1. Click `.anticon-more` in MEETING DONE row REQ-00073.</t>
+  </si>
+  <si>
+    <t>Dropdown opens with the same single "Capture VC Outcome" item — menu does not vary by row status.</t>
+  </si>
+  <si>
+    <t>SM-FS-CBR §4.2 + Arch. Correction</t>
+  </si>
+  <si>
+    <t>`callback-row-more-menu-meetingdone.png`</t>
+  </si>
+  <si>
+    <t>TC_CBR_FUNC_027</t>
+  </si>
+  <si>
+    <t>"Capture VC Outcome" menu click opens modal — PENDING row context</t>
+  </si>
+  <si>
+    <t>PENDING row more menu open</t>
+  </si>
+  <si>
+    <t>1. Click "Capture VC Outcome". 2. Inspect modal.</t>
+  </si>
+  <si>
+    <t>Ant Modal opens (smaller than details drawer). Title "Capture VC Outcome" centered. Static header displays `Registration No: GHNG-…` and `Customer Name: …` read from the source row. Field labelled "Select Outcome:" with placeholder "Please select an outcome". Buttons: Cancel (outlined) + Submit (primary, disabled).</t>
+  </si>
+  <si>
+    <t>SM-FS-CBR §4.5</t>
+  </si>
+  <si>
+    <t>`callback-capture-vc-outcome-pending.png`</t>
+  </si>
+  <si>
+    <t>TC_CBR_FUNC_028</t>
+  </si>
+  <si>
+    <t>"Capture VC Outcome" modal can be opened on MEETING DONE row (re-capture)</t>
+  </si>
+  <si>
+    <t>MEETING DONE row more menu open</t>
+  </si>
+  <si>
+    <t>1. Click "Capture VC Outcome" on REQ-00073.</t>
+  </si>
+  <si>
+    <t>Same modal opens with Registration No GHNG-2000000009 + Customer Name pre-filled. Outcome can be re-captured for already-MEETING-DONE rows.</t>
+  </si>
+  <si>
+    <t>SM-FS-CBR §4.2 (preconditions)</t>
+  </si>
+  <si>
+    <t>`callback-capture-vc-outcome-meetingdone.png`</t>
+  </si>
+  <si>
+    <t>TC_CBR_FUNC_029</t>
+  </si>
+  <si>
+    <t>Outcome dropdown exposes exactly 10 vcOutcome codes</t>
+  </si>
+  <si>
+    <t>Capture VC Outcome modal open</t>
+  </si>
+  <si>
+    <t>1. Click the "Select Outcome:" Ant Select.</t>
+  </si>
+  <si>
+    <t>Dropdown opens. Exactly 10 options in this order: (1) VC Done with Preference, (2) VC Done, No Preference, (3) Future Scheduled, (4) Future Rescheduled, (5) Missed Scheduled NC, (6) Not Interested, Lost, (7) Never Connected, (8) TL Lost, (9) VC 2-Done, (10) CP to Drive Preference.</t>
+  </si>
+  <si>
+    <t>SM-FS-CBR §4.3; SM-WF-CBR §4</t>
+  </si>
+  <si>
+    <t>`callback-vc-outcome-dropdown.png`</t>
+  </si>
+  <si>
+    <t>TC_CBR_VAL_030</t>
+  </si>
+  <si>
+    <t>Submit disabled while no outcome selected</t>
+  </si>
+  <si>
+    <t>Modal open, dropdown not yet picked</t>
+  </si>
+  <si>
+    <t>1. Open Capture VC Outcome modal. 2. Inspect Submit button state without picking an outcome.</t>
+  </si>
+  <si>
+    <t>Submit button is disabled (`disabled` attribute or `ant-btn-disabled` class). No inline error message is surfaced.</t>
+  </si>
+  <si>
+    <t>SM-FS-CBR §4.4 BR1</t>
+  </si>
+  <si>
+    <t>`callback-capture-vc-outcome-validation.png`</t>
+  </si>
+  <si>
+    <t>TC_CBR_FUNC_031</t>
+  </si>
+  <si>
+    <t>Selecting any outcome enables Submit</t>
+  </si>
+  <si>
+    <t>1. Open dropdown. 2. Click "VC Done, No Preference". 3. Inspect Submit.</t>
+  </si>
+  <si>
+    <t>Selected outcome label displayed in select trigger. Submit button becomes enabled.</t>
+  </si>
+  <si>
+    <t>TC_CBR_BIZ_032</t>
+  </si>
+  <si>
+    <t>Submitting "VC Done with Preference" triggers VC_REQUEST offer</t>
+  </si>
+  <si>
+    <t>Modal open on a row in CONFIRMED/MEETING DONE state; buyer exists</t>
+  </si>
+  <si>
+    <t>1. Select "VC Done with Preference". 2. Click Submit.</t>
+  </si>
+  <si>
+    <t>Modal closes. Backend records vcOutcome = VC_DONE_PREFERENCE. Per SM-WF-CBR §4 and §6 BR5, a VC_REQUEST discount offer is automatically created for the buyer. (Verification done downstream in Offers / DB.) Row's VC Outcome column updates to "VC Done with Preference".</t>
+  </si>
+  <si>
+    <t>SM-WF-CBR §6 BR5; SM-FS-CBR §4.4 BR2</t>
+  </si>
+  <si>
+    <t>TC_CBR_BIZ_033</t>
+  </si>
+  <si>
+    <t>Submitting "VC 2-Done" triggers VC_REQUEST offer</t>
+  </si>
+  <si>
+    <t>Modal open on a row that has had at least one prior VC</t>
+  </si>
+  <si>
+    <t>1. Select "VC 2-Done". 2. Click Submit.</t>
+  </si>
+  <si>
+    <t>Same as TC_CBR_BIZ_032 — VC_REQUEST offer auto-created. Per SM-WF-CBR §4 table: VC_2_DONE is the second outcome (alongside VC_DONE_PREFERENCE) that triggers the offer.</t>
+  </si>
+  <si>
+    <t>SM-WF-CBR §6 BR5</t>
+  </si>
+  <si>
+    <t>TC_CBR_BIZ_034</t>
+  </si>
+  <si>
+    <t>Submitting outcomes other than VC_DONE_PREFERENCE / VC_2_DONE does NOT trigger VC_REQUEST</t>
+  </si>
+  <si>
+    <t>1. Select "VC Done, No Preference". 2. Click Submit. 3. Repeat for "Not Interested, Lost", "Never Connected", "TL Lost", "Missed Scheduled NC", "Future Scheduled", "Future Rescheduled", "CP to Drive Preference".</t>
+  </si>
+  <si>
+    <t>For each of these 8 outcomes, no VC_REQUEST offer is created for the buyer. Outcome is recorded on the row.</t>
+  </si>
+  <si>
+    <t>SM-WF-CBR §4 table (Triggers VC_REQUEST? column = No)</t>
+  </si>
+  <si>
+    <t>TC_CBR_BIZ_035</t>
+  </si>
+  <si>
+    <t>COMPLETED status is not reachable via UI (FSD-CORRECTION)</t>
+  </si>
+  <si>
+    <t>Any row in any status</t>
+  </si>
+  <si>
+    <t>1. Capture outcome on any row. 2. Trigger buyer feedback submission (out of scope here). 3. Inspect Status column for the row.</t>
+  </si>
+  <si>
+    <t>Status badge never displays "COMPLETED". Per FSD-CORRECTION 2026-05-25 at `callback-request-sm.service.js:78-87`, the service catches ENUM truncation and falls back to CONFIRMED. Documentation gap retained but is not testable as reachable.</t>
+  </si>
+  <si>
+    <t>SM-FS-CBR §1.5 + FSD-CORRECTION; SM-WF-CBR §3</t>
+  </si>
+  <si>
+    <t>`callback-details-drawer-meetingdone.png` (shows CONFIRMED for what would be COMPLETED)</t>
+  </si>
+  <si>
+    <t>TC_CBR_FUNC_036</t>
+  </si>
+  <si>
+    <t>Cancel button in VC Outcome modal closes modal without submission</t>
+  </si>
+  <si>
+    <t>1. Open modal. 2. Click Cancel (outlined).</t>
+  </si>
+  <si>
+    <t>Modal closes. Row's VC Outcome column unchanged. No backend write.</t>
+  </si>
+  <si>
+    <t>TC_CBR_FUNC_037</t>
+  </si>
+  <si>
+    <t>"Create Callback Request" button opens the create drawer</t>
+  </si>
+  <si>
+    <t>1. Click `button:has-text("Create Callback Request")`.</t>
+  </si>
+  <si>
+    <t>Right-side drawer opens with title "Create Callback Request". Buyer search input visible. Four form fields (buyerEmail, managerEmail, ccEmails, requestedAt) are DISABLED until a buyer is selected.</t>
+  </si>
+  <si>
+    <t>SM-FS-CBR §5.1 / §5.3</t>
+  </si>
+  <si>
+    <t>`callback-create-drawer.png`</t>
+  </si>
+  <si>
+    <t>TC_CBR_FUNC_038</t>
+  </si>
+  <si>
+    <t>Buyer search returns results table with radio selection</t>
+  </si>
+  <si>
+    <t>Create drawer open</t>
+  </si>
+  <si>
+    <t>1. Type "Anjali" into `.ant-drawer input[type="search"]`. 2. Click `.ant-drawer button:has-text("Search")`.</t>
+  </si>
+  <si>
+    <t>Results table renders with 5 columns: Registration Number, Name, Previous Callbacks, Email, Phone. Each row has a radio input. Pagination footer reads "1-10 of 55 items" (or similar).</t>
+  </si>
+  <si>
+    <t>SM-FS-CBR §5.3 (Customer required field)</t>
+  </si>
+  <si>
+    <t>`callback-create-drawer-searched.png`</t>
+  </si>
+  <si>
+    <t>TC_CBR_FUNC_039</t>
+  </si>
+  <si>
+    <t>Selecting buyer radio auto-populates buyerEmail and managerEmail (readonly)</t>
+  </si>
+  <si>
+    <t>Search results visible</t>
+  </si>
+  <si>
+    <t>1. Click the radio in any results row.</t>
+  </si>
+  <si>
+    <t>`input#buyerEmail` auto-populates with the buyer's registered email (e.g., test@gmail.com). `input#managerEmail` auto-populates with the assigned SM's email (e.g., test2@test.com). Both remain readonly. CC and Date fields become editable.</t>
+  </si>
+  <si>
+    <t>SM-FS-CBR §5.3</t>
+  </si>
+  <si>
+    <t>`callback-create-buyer-selected.png`</t>
+  </si>
+  <si>
+    <t>TC_CBR_VAL_040</t>
+  </si>
+  <si>
+    <t>Create button stays disabled until date is picked</t>
+  </si>
+  <si>
+    <t>Buyer selected, date empty</t>
+  </si>
+  <si>
+    <t>1. Skip the Date picker. 2. Click `.ant-drawer button:has-text("Create")` (if clickable) or inspect its disabled state.</t>
+  </si>
+  <si>
+    <t>Create button is and remains disabled while `input#requestedAt` is empty. No `.ant-form-item-explain-error` inline error appears — form gates solely via the disabled state.</t>
+  </si>
+  <si>
+    <t>SM-FS-CBR §5.3 (Date required)</t>
+  </si>
+  <si>
+    <t>`callback-create-drawer-validation.png`</t>
+  </si>
+  <si>
+    <t>TC_CBR_FUNC_041</t>
+  </si>
+  <si>
+    <t>CC field is a multi-tag Ant Select</t>
+  </si>
+  <si>
+    <t>Buyer selected</t>
+  </si>
+  <si>
+    <t>1. Inspect `input#ccEmails`. 2. Type an email, press Enter.</t>
+  </si>
+  <si>
+    <t>Field is `type=search` multi-tag Ant Select with placeholder "Add CC emails". Each Enter creates a tag. Multiple CC addresses can be added.</t>
+  </si>
+  <si>
+    <t>SM-FS-CBR §2.3 (CC Email Addresses) — exposed in Create flow</t>
+  </si>
+  <si>
+    <t>TC_CBR_FUNC_042</t>
+  </si>
+  <si>
+    <t>Selecting a date enables Create button</t>
+  </si>
+  <si>
+    <t>Buyer selected; CC may be empty</t>
+  </si>
+  <si>
+    <t>1. Click `input#requestedAt`. 2. Pick a future date and time. 3. Inspect Create button.</t>
+  </si>
+  <si>
+    <t>Create button becomes enabled (primary).</t>
+  </si>
+  <si>
+    <t>TC_CBR_BIZ_043</t>
+  </si>
+  <si>
+    <t>Create submits request with status REQUESTED + least-loaded SM assignment</t>
+  </si>
+  <si>
+    <t>All required fields valid</t>
+  </si>
+  <si>
+    <t>1. Submit a fully-populated form.</t>
+  </si>
+  <si>
+    <t>Drawer closes. New row appears in the table with status badge mapped to backend "REQUESTED" (UI label). Per SM-FS-CBR §1.7 BR4 (FSD-CORRECTION 2026-05-25) the system uses **least-loaded** algorithm, NOT round-robin (round-robin code is disabled at `callback-request-sm.service.js:338-349`). If creator is SM Admin, managerId = their own ID (no auto-distribute).</t>
+  </si>
+  <si>
+    <t>SM-FS-CBR §1.7 BR4 + FSD-CORRECTION; SM-FS-CBR §5.4</t>
+  </si>
+  <si>
+    <t>TC_CBR_BIZ_044</t>
+  </si>
+  <si>
+    <t>SM with isAvailable=false is excluded from auto-assignment pool</t>
+  </si>
+  <si>
+    <t>Backend SM list includes one SM flagged `isAvailable = false`</t>
+  </si>
+  <si>
+    <t>1. Submit a new Create Callback Request via the create drawer. 2. Observe Manager column on the new row.</t>
+  </si>
+  <si>
+    <t>The newly assigned manager is one of the SMs with `isAvailable = true`. The unavailable SM does not receive new assignments.</t>
+  </si>
+  <si>
+    <t>SM-FS-CBR §1.7 BR5; SM-WF-CBR §6 BR2</t>
+  </si>
+  <si>
+    <t>`callback-loaded.png` (table Manager column)</t>
+  </si>
+  <si>
+    <t>TC_CBR_FUNC_045</t>
+  </si>
+  <si>
+    <t>Cancel in Create drawer dismisses without saving</t>
+  </si>
+  <si>
+    <t>Create drawer open with any state</t>
+  </si>
+  <si>
+    <t>1. Click Cancel button in the drawer footer.</t>
+  </si>
+  <si>
+    <t>Drawer closes. No new row added to the table. No backend write.</t>
+  </si>
+  <si>
+    <t>SM-FS-CBR §5</t>
+  </si>
+  <si>
+    <t>TC_CBR_FUNC_046</t>
+  </si>
+  <si>
+    <t>Empty state shown when search yields zero rows</t>
+  </si>
+  <si>
+    <t>1. Search a string that matches nothing.</t>
+  </si>
+  <si>
+    <t>Ant empty illustration rendered ("No data") + counter "Total 0 Callback Requests". No table rows.</t>
+  </si>
+  <si>
+    <t>TC_CBR_NEG_047</t>
+  </si>
+  <si>
+    <t>Submit in modal cannot be triggered programmatically while outcome empty</t>
+  </si>
+  <si>
+    <t>Modal open, no outcome</t>
+  </si>
+  <si>
+    <t>1. Inspect Submit button DOM. 2. Attempt keyboard `Enter` on the modal without picking an outcome.</t>
+  </si>
+  <si>
+    <t>Submit remains disabled. Enter key does not submit the form. No backend POST is fired. No silent submission.</t>
+  </si>
+  <si>
+    <t>TC_CBR_NEG_048</t>
+  </si>
+  <si>
+    <t>Create button cannot be triggered while date empty</t>
+  </si>
+  <si>
+    <t>1. Press Enter in CC field while date empty. 2. Inspect Create button + network panel.</t>
+  </si>
+  <si>
+    <t>Form does not submit. No POST to `/callback-request` endpoint. Create button stays disabled.</t>
+  </si>
+  <si>
+    <t>TC_CBR_NEG_049</t>
+  </si>
+  <si>
+    <t>Eye icon on a row does NOT expose any SM action surface</t>
+  </si>
+  <si>
+    <t>Any row</t>
+  </si>
+  <si>
+    <t>1. Click `.anticon-eye`. 2. Inspect drawer for action buttons.</t>
+  </si>
+  <si>
+    <t>Details drawer is purely read-only. No "Schedule Meeting", no "Confirm Meeting", no "Record Outcome", no edit affordance. Only the close button is interactive. The only place where an SM records an outcome is via the more menu → Capture VC Outcome modal.</t>
+  </si>
+  <si>
+    <t>Arch. Correction; SM-FS-CBR §1.4</t>
+  </si>
+  <si>
+    <t>`callback-details-drawer-pending.png`, `callback-details-drawer-meetingdone.png`</t>
+  </si>
+  <si>
+    <t>TC_CBR_EDGE_050</t>
+  </si>
+  <si>
+    <t>Modal Registration No and Customer Name match the row that opened it</t>
+  </si>
+  <si>
+    <t>1. Note Registration No and Customer Name of row X. 2. Click more → Capture VC Outcome on row X. 3. Inspect modal header.</t>
+  </si>
+  <si>
+    <t>Modal header shows `Registration No: &lt;row X reg no&gt;` and `Customer Name: &lt;row X name&gt;`. Values match exactly — modal scope is per-row.</t>
+  </si>
+  <si>
+    <t>TC_CBR_EDGE_051</t>
+  </si>
+  <si>
+    <t>Status filter clears restores all rows</t>
+  </si>
+  <si>
+    <t>Status filter applied</t>
+  </si>
+  <si>
+    <t>1. Open status filter. 2. Uncheck all options. 3. Apply.</t>
+  </si>
+  <si>
+    <t>All rows return regardless of status. Filter trigger no longer shows "active" indicator.</t>
+  </si>
+  <si>
+    <t>TC_CBR_EDGE_052</t>
+  </si>
+  <si>
+    <t>Date range pickers Start &gt; End reject the range</t>
+  </si>
+  <si>
+    <t>1. Pick a Start Date in future. 2. Try to pick an End Date earlier than Start.</t>
+  </si>
+  <si>
+    <t>Ant DatePicker blocks End Date &lt; Start Date selection (greyed-out calendar dates). Table is not corrupted into an invalid filtered state.</t>
+  </si>
+  <si>
+    <t>TC_CBR_EDGE_053</t>
+  </si>
+  <si>
+    <t>Refresh preserves active search text and filters</t>
+  </si>
+  <si>
+    <t>Search applied + Status filter applied</t>
+  </si>
+  <si>
+    <t>1. Apply search + status filter. 2. Click Refresh.</t>
+  </si>
+  <si>
+    <t>After reload, search text retained in the search input, and status filter chip / state retained. Filtered subset shown.</t>
+  </si>
+  <si>
+    <t>TC_CBR_BIZ_054</t>
+  </si>
+  <si>
+    <t>SM (non-admin) sees only own assigned requests</t>
+  </si>
+  <si>
+    <t>Two test users: a regular SM and an SM Admin</t>
+  </si>
+  <si>
+    <t>1. Login as regular SM Tester. 2. Inspect Manager column values across all visible rows.</t>
+  </si>
+  <si>
+    <t>All visible rows have Manager column = current SM's name. SM Admin login (separate test) sees rows with varied Manager values across all SMs.</t>
+  </si>
+  <si>
+    <t>SM-FS-CBR §1.7 BR1, BR2; SM-WF-CBR §6 BR9</t>
+  </si>
+  <si>
+    <t>`callback-loaded.png` (Manager column)</t>
+  </si>
+  <si>
+    <t>TC_CBR_BIZ_055</t>
+  </si>
+  <si>
+    <t>"VC Done with Preference" outcome syncs to LeadSquared (out-of-scope confirmation)</t>
+  </si>
+  <si>
+    <t>LSQ excluded from QA scope per CLAUDE.md Constraint 1</t>
+  </si>
+  <si>
+    <t>1. Submit VC_DONE_PREFERENCE outcome via the modal.</t>
+  </si>
+  <si>
+    <t>Per SM-FS-CBR §1.8 and §4.4 BR3, VC outcome is synced to LeadSquared CRM. **LSQ is excluded from QA scope** (CLAUDE.md Constraint 1) — this TC is documented for traceability only. Verification limited to portal-side row update; LSQ side is NOT tested.</t>
+  </si>
+  <si>
+    <t>SM-FS-CBR §1.8, §4.4 BR3 + CLAUDE.md Constraint 1</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_UI_001</t>
+  </si>
+  <si>
+    <t>Page heading and sidebar selection render on Physical Allocation landing</t>
+  </si>
+  <si>
+    <t>SM logged in (sales-manager.json session); active PHYSICAL_EVENT campaign in UAT</t>
+  </si>
+  <si>
+    <t>1. Navigate to `https://uat-web.xrportal.in/sales-manager/physical-allocation`. 2. Wait for `networkidle`. 3. Assert `h5:has-text("Physical Unit Allocation")` is visible inside `.header-admin.new-header-text`. 4. Assert sidebar `Allocation` nav item carries the green-fill selected state.</t>
+  </si>
+  <si>
+    <t>Page heading "Physical Unit Allocation" is rendered. Sidebar shows three nav items (Callback Requests, Towers, Allocation) with `Allocation` highlighted as the active tile.</t>
+  </si>
+  <si>
+    <t>SM-BRD §3 (module list), SM-FS §1.1, SM-FS §1.4</t>
+  </si>
+  <si>
+    <t>`allocation-loaded-active.png`</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_UI_002</t>
+  </si>
+  <si>
+    <t>Active-campaign landing shows enabled search input and Scan QR button</t>
+  </si>
+  <si>
+    <t>SM logged in; active PHYSICAL_EVENT campaign (`status=RUNNING`)</t>
+  </si>
+  <si>
+    <t>1. Navigate to `/sales-manager/physical-allocation`. 2. Wait for `GET /api/v1/sales-manager/physical-event/campaign/active` to settle. 3. Assert `input.search-input` is rendered, has placeholder `Search by Phone or Registration Number...`, and `disabled` attribute is `false`. 4. Assert `button:has-text("Scan QR")` is rendered and `disabled` attribute is `false`. 5. Assert no `🏢 No Active Campaign` empty-state card is present.</t>
+  </si>
+  <si>
+    <t>Search input and Scan QR button are both enabled. The "No Active Campaign" empty-state card is absent. The campaign name is intentionally not rendered anywhere on the page — enablement of these controls is the only visual confirmation that a campaign is active.</t>
+  </si>
+  <si>
+    <t>SM-BRD §4.5 (PHYSICAL_EVENT only), SM-FS §1.3, SM-FS §1.5 #1</t>
+  </si>
+  <si>
+    <t>`allocation-loaded-active.png`, `allocation-search-form.png`</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_UI_003</t>
+  </si>
+  <si>
+    <t>No Active Campaign idle state — controls disabled</t>
+  </si>
+  <si>
+    <t>SM logged in; NO PHYSICAL_EVENT campaign currently RUNNING in UAT</t>
+  </si>
+  <si>
+    <t>1. Navigate to `/sales-manager/physical-allocation` when no campaign is RUNNING. 2. Wait for `GET /campaign/active` to return null/non-RUNNING. 3. Assert the `🏢 No Active Campaign` empty-state card is rendered. 4. Assert `input.search-input` has `disabled=true`. 5. Assert `button:has-text("Scan QR")` has `disabled=true`.</t>
+  </si>
+  <si>
+    <t>The "No Active Campaign" empty-state card is visible. Both the search input and Scan QR button render but are disabled — SM cannot initiate a search until a campaign goes RUNNING.</t>
+  </si>
+  <si>
+    <t>SM-BRD §4.5, SM-FS §1.3, SM-FS §1.5 #1, SM-WF §7 step 1</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_UI_004</t>
+  </si>
+  <si>
+    <t>Search card structural elements — input + Scan QR layout</t>
+  </si>
+  <si>
+    <t>SM logged in; active campaign</t>
+  </si>
+  <si>
+    <t>1. Navigate to `/sales-manager/physical-allocation`. 2. Locate `.search-card`. 3. Assert it contains exactly one `&lt;Row&gt;` with two cols. 4. Left col contains `input.search-input` (Ant Design large input). 5. Right col contains `button:has-text("Scan QR")` with QR-code icon (`QrcodeOutlined`).</t>
+  </si>
+  <si>
+    <t>Search card renders with input on the left, Scan QR button on the right. Both elements share the `large` Ant Design size.</t>
+  </si>
+  <si>
+    <t>SM-FS §1.4</t>
+  </si>
+  <si>
+    <t>`allocation-search-form.png`</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_FUNC_005</t>
+  </si>
+  <si>
+    <t>Search by phone — debounce threshold (less than 5 chars triggers no API call)</t>
+  </si>
+  <si>
+    <t>SM logged in; active campaign; search input enabled</t>
+  </si>
+  <si>
+    <t>1. Focus `input.search-input`. 2. Type `8888` (4 characters). 3. Wait 1.5s (well over 500 ms debounce). 4. Assert no `GET /api/v1/sales-manager/physical-event/search` request was fired in the network log. 5. Assert results table (`.ant-table`) is not mounted in `.search-card`.</t>
+  </si>
+  <si>
+    <t>No API call is triggered while the input length is less than 5. The results table does not render. (Source: `handleSearch` invokes `performSearch` only when `query.trim().length &gt;= 5`.)</t>
+  </si>
+  <si>
+    <t>SM-FS §1.6 #1, SM-FS §1.4</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_FUNC_006</t>
+  </si>
+  <si>
+    <t>Search by phone — exactly 5 chars triggers API call after 500 ms debounce</t>
+  </si>
+  <si>
+    <t>1. Focus `input.search-input`. 2. Type `88888` (5 characters). 3. Wait 500 ms + network round-trip. 4. Capture the network call `GET /api/v1/sales-manager/physical-event/search?campaignId=295&amp;q=88888`. 5. Assert the results table mounts as a child Row of `.search-card`.</t>
+  </si>
+  <si>
+    <t>A single search API call fires after the 500 ms debounce window with `campaignId=295` and `q=88888`. The results table renders with documented column headers.</t>
+  </si>
+  <si>
+    <t>SM-FS §1.6 #1</t>
+  </si>
+  <si>
+    <t>`allocation-search-result.png`</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_FUNC_007</t>
+  </si>
+  <si>
+    <t>Results table headers render in documented order</t>
+  </si>
+  <si>
+    <t>SM logged in; active campaign; search executed (≥5 chars)</t>
+  </si>
+  <si>
+    <t>1. Type any 10-digit phone (e.g. `8888888888`) into the search input. 2. Wait for results table to mount. 3. Read header cells `.ant-table-thead th` in DOM order. 4. Assert they are exactly: `Customer Name`, `Phone Number`, `Registration Numbers`, `Registration Count`, `Action`.</t>
+  </si>
+  <si>
+    <t>The results table renders with the five hard-coded columns in the order Customer Name → Phone Number → Registration Numbers → Registration Count → Action. The Action column is fixed right and centre-aligned.</t>
+  </si>
+  <si>
+    <t>SM-FS §1.4, SM-FS §1.6 #2</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_FUNC_008</t>
+  </si>
+  <si>
+    <t>Search returns no buyers registered for active campaign — "No data" empty state</t>
+  </si>
+  <si>
+    <t>SM logged in; active campaign id=295; no buyer registrations seeded against it (current UAT state)</t>
+  </si>
+  <si>
+    <t>1. Type `8888888888` into the search input. 2. Wait for the search API call to resolve. 3. Inspect the table body. 4. Assert `.ant-empty-description` contains text `No data`. 5. Assert no `tr.ant-table-row` elements are mounted in `.ant-table-tbody`.</t>
+  </si>
+  <si>
+    <t>The Ant Design default empty-state is shown with the text "No data" inside `.ant-empty-description`. No customer rows render because no buyer registrations exist against campaign 295 in UAT.</t>
+  </si>
+  <si>
+    <t>SM-FS §1.5 #4 ("No records found" rule), SM-FS §1.6</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_FUNC_009</t>
+  </si>
+  <si>
+    <t>Non-matching alphanumeric query — same "No data" empty state</t>
+  </si>
+  <si>
+    <t>1. Type `ZZNOTFOUND` (10 chars, no match) into `input.search-input`. 2. Wait for the search API to resolve. 3. Assert `.ant-empty-description :text("No data")` is visible. 4. Confirm response payload `data: []`.</t>
+  </si>
+  <si>
+    <t>The client renders the identical "No data" empty-state row regardless of query content. This confirms the empty rendering is uniform whether the query returns zero rows for a valid phone (TC_008) or a clearly bogus string.</t>
+  </si>
+  <si>
+    <t>SM-FS §1.5 #4</t>
+  </si>
+  <si>
+    <t>`allocation-search-no-result.png`</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_FUNC_010</t>
+  </si>
+  <si>
+    <t>Clearing the search input unmounts the results table</t>
+  </si>
+  <si>
+    <t>SM logged in; active campaign; a prior search has been executed and table is mounted</t>
+  </si>
+  <si>
+    <t>1. Confirm `.ant-table` is currently mounted in `.search-card`. 2. Triple-click the input to select all, then press `Backspace` (or fire input event with empty string). 3. Assert `searchValue.length === 0`. 4. Assert `.ant-table` is no longer present in the DOM.</t>
+  </si>
+  <si>
+    <t>When the input is cleared, the results table is immediately unmounted and `searchResults` state is reset to empty. (Source: `handleSearch` clears state on empty input.)</t>
+  </si>
+  <si>
+    <t>SM-FS §1.6</t>
+  </si>
+  <si>
+    <t>`allocation-loaded-active.png` (table-absent state)</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_FUNC_011</t>
+  </si>
+  <si>
+    <t>Scan QR button is rendered and clickable on active campaign</t>
+  </si>
+  <si>
+    <t>1. Locate `button:has-text("Scan QR")`. 2. Assert visible and enabled. 3. Click it. 4. Assert `QrScannerModal` mounts (camera-permission dialog or `.qr-scanner-modal` container, per source import).</t>
+  </si>
+  <si>
+    <t>The Scan QR button opens the QR Scanner modal for camera-based registration lookup. (Note: actual camera capture is out of scope for this TC; only modal mount is asserted.)</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_FUNC_012</t>
+  </si>
+  <si>
+    <t>Search API includes correct `campaignId` query param</t>
+  </si>
+  <si>
+    <t>SM logged in; active campaign id=295</t>
+  </si>
+  <si>
+    <t>1. Open the network panel. 2. Type `8888888888` into the search input. 3. Capture the search request URL. 4. Assert URL matches `https://uat-api.xrportal.in/api/v1/sales-manager/physical-event/search?campaignId=295&amp;q=8888888888` (order of params may vary; both keys must be present).</t>
+  </si>
+  <si>
+    <t>The search call is parameterised with both `campaignId` (the active campaign's id from `/campaign/active`) and `q` (the typed query). Searching is always scoped to the currently active campaign.</t>
+  </si>
+  <si>
+    <t>SM-FS §1.6 #1, SM-BRD §4.5</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_NEG_013</t>
+  </si>
+  <si>
+    <t>Direct navigation to `/checkout` without selecting a customer redirects to landing</t>
+  </si>
+  <si>
+    <t>SM logged in; active campaign; fresh tab (no React Router state)</t>
+  </si>
+  <si>
+    <t>1. Navigate directly to `https://uat-web.xrportal.in/sales-manager/physical-allocation/checkout`. 2. Wait up to 1 s. 3. Assert URL has redirected to `/sales-manager/physical-allocation`. 4. Assert the landing page (search card) is shown.</t>
+  </si>
+  <si>
+    <t>The `UnitAllocationPage` guard (`if (!customer</t>
+  </si>
+  <si>
+    <t>!campaign) navigate('/sales-manager/physical-allocation')`) fires synchronously on mount. The redirect happens within ~500 ms and the SM is returned to the search landing.</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_NEG_014</t>
+  </si>
+  <si>
+    <t>Direct navigation to `/kyc` without checkout context renders blank</t>
+  </si>
+  <si>
+    <t>SM logged in; active campaign; no `location.state.customerContext`</t>
+  </si>
+  <si>
+    <t>1. Navigate directly to `/sales-manager/physical-allocation/kyc`. 2. Wait 1 s. 3. Assert URL remains `/sales-manager/physical-allocation/kyc` (no redirect). 4. Assert document body is empty — no headings, inputs, or content (white viewport).</t>
+  </si>
+  <si>
+    <t>The `KycPage` destructures `customerContext` from `location.state</t>
+  </si>
+  <si>
+    <t>{}`; with `undefined`, `fetchApplicants()` short-circuits and no UI mounts. The URL stays on `/kyc` but the page renders blank (different behaviour from the checkout redirect).</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_E2E_015</t>
+  </si>
+  <si>
+    <t>End-to-end — customer search → select → checkout transition</t>
+  </si>
+  <si>
+    <t>SM logged in; active PHYSICAL_EVENT campaign; at least one buyer registration seeded against campaign id=295; buyer has active `registrationCount &gt;= 1`</t>
+  </si>
+  <si>
+    <t>1. Navigate to `/sales-manager/physical-allocation`. 2. Type the seeded buyer's phone (10 chars) into `input.search-input`. 3. Wait for `.ant-table-tbody tr.ant-table-row` to mount with the buyer's data. 4. Assert columns populate: Customer Name, Phone Number, Registration Numbers (comma-joined), Registration Count. 5. Click `button.select-action-btn` (or `button:has-text("Select")`) in the row. 6. Assert URL changes to `/sales-manager/physical-allocation/checkout`. 7. Assert the `UnitAllocationPage` mounts (TowerHeatmap visible).</t>
+  </si>
+  <si>
+    <t>After selecting a customer row, the SM is navigated to `/checkout` with `location.state.customer = record` and `location.state.campaign = activeCampaign`. The Unit Allocation page renders with the TowerHeatmap component.</t>
+  </si>
+  <si>
+    <t>SM-FS §1.6 #3, SM-FS §2.1-2.2, SM-WF §7 steps 3-4</t>
+  </si>
+  <si>
+    <t>`[STUB-EVIDENCE]` — no current screenshot; route reachable only after data seed</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_E2E_016</t>
+  </si>
+  <si>
+    <t>Checkout — Tower heatmap, Floor &amp; Unit Plan, Cost Sheet, Payment Schedule visible</t>
+  </si>
+  <si>
+    <t>TC_015 prerequisites + SM on `/checkout` with valid context</t>
+  </si>
+  <si>
+    <t>1. After TC_015 step 7, assert `TowerHeatmap` component is rendered. 2. Click button labelled `Floor &amp; Unit Plan` and assert `FloorUnitPlan` panel opens. 3. Click `Cost Sheet` and assert cost breakdown drawer/panel renders the documented fields (Unit number, Floor, Tower, Typology, Carpet area, Agreement value, Allocation amount, GST, Discounts, All Inclusive Price). 4. Click `Payment Schedule` and assert milestone payment table renders.</t>
+  </si>
+  <si>
+    <t>All four checkout views (Tower heatmap, Floor &amp; Unit Plan, Cost Sheet, Payment Schedule) render correctly. Cost Sheet line items match the BRD-documented schema.</t>
+  </si>
+  <si>
+    <t>SM-FS §2.3, SM-FS "How to Use" Step 1</t>
+  </si>
+  <si>
+    <t>`[STUB-EVIDENCE]` — checkout state requires real customer context</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_E2E_017</t>
+  </si>
+  <si>
+    <t>Unit selection places 20-minute HOLD via Redis</t>
+  </si>
+  <si>
+    <t>TC_016 prerequisites; an AVAILABLE unit exists for buyer's typology</t>
+  </si>
+  <si>
+    <t>1. From the Tower heatmap, click an AVAILABLE (green) unit cell. 2. Assert the `UnitDetail` drawer (Ant `Drawer`) opens. 3. Click the confirm/select-unit button. 4. Capture the WebSocket message `unit_hold_started` (or equivalent) and assert the unit status flips to HOLD (yellow). 5. Confirm a 20-minute countdown timer is visible.</t>
+  </si>
+  <si>
+    <t>The selected unit transitions from AVAILABLE → HOLD. A 20-minute timer starts. Other connected sessions (broadcast via `useWebSocket`) should see the same status change.</t>
+  </si>
+  <si>
+    <t>SM-FS §2.5 #1-3, SM-WF §7 step 5, SM-WF §8 (Unit Hold Rules)</t>
+  </si>
+  <si>
+    <t>`[STUB-EVIDENCE]` — requires real unit + open campaign + non-destructive dry-run path</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_E2E_018</t>
+  </si>
+  <si>
+    <t>Hold expiry after 20 minutes returns unit to AVAILABLE</t>
+  </si>
+  <si>
+    <t>TC_017 unit on HOLD with active 20-minute timer</t>
+  </si>
+  <si>
+    <t>1. Place a unit on HOLD (TC_017). 2. Do not initiate payment. 3. Wait beyond 20 minutes (or simulate via cron). 4. Refresh `/checkout`. 5. Assert the unit's status has reverted to AVAILABLE (green).</t>
+  </si>
+  <si>
+    <t>The cron releases stale HOLDs older than 20 minutes. After expiry, the unit becomes AVAILABLE again and can be re-selected.</t>
+  </si>
+  <si>
+    <t>SM-FS §2.5 #2, SM-WF §8</t>
+  </si>
+  <si>
+    <t>`[STUB-EVIDENCE]` — long-running, requires test environment with controllable cron</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_FUNC_019</t>
+  </si>
+  <si>
+    <t>Online payment — QR code scanner modal opens from checkout</t>
+  </si>
+  <si>
+    <t>TC_017 unit on HOLD</t>
+  </si>
+  <si>
+    <t>1. After holding a unit, click the QR code payment option. 2. Assert `QrScannerModal` opens displaying a QR code image. 3. Assert helper text instructs the customer to scan from their device.</t>
+  </si>
+  <si>
+    <t>The QR scanner modal opens with a payable QR code. Customer can scan with their phone to be redirected to Easebuzz/Razorpay.</t>
+  </si>
+  <si>
+    <t>SM-FS §2.4 (online QR), SM-WF §7 step 6</t>
+  </si>
+  <si>
+    <t>`[STUB-EVIDENCE]` — requires real customer context + held unit</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_FUNC_020</t>
+  </si>
+  <si>
+    <t>Offline payment — OfflinePaymentDrawer requires reference, amount, date, proof</t>
+  </si>
+  <si>
+    <t>1. Click `Record Offline Payment`. 2. Assert `OfflinePaymentDrawer` opens. 3. Click Submit with all fields empty — assert submission blocked and field-level errors render on `referenceNumber`, `amount`, `date`, and `proofDocument`. 4. Fill all four fields with valid data and upload a proof file. 5. Click Submit — assert request fires and drawer closes.</t>
+  </si>
+  <si>
+    <t>The OfflinePaymentDrawer enforces all four mandatory fields (reference number, amount, date, proof upload). Submission is blocked until all four are valid.</t>
+  </si>
+  <si>
+    <t>SM-FS §2.4 (offline), SM-FS §2.5 #4</t>
+  </si>
+  <si>
+    <t>`[STUB-EVIDENCE]` — requires real checkout context</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_E2E_021</t>
+  </si>
+  <si>
+    <t>Payment success → unit BOOKED → registration WINNER → navigate to KYC</t>
+  </si>
+  <si>
+    <t>TC_019 or TC_020 payment initiated and confirmed</t>
+  </si>
+  <si>
+    <t>1. Complete a successful payment (QR or offline). 2. Wait for the payment webhook → server confirmation. 3. Assert unit status flips from HOLD → BOOKED (red per source `getStatusColor`). 4. Assert backend registration status updates to WINNER (verify via DB or API). 5. Assert SM is redirected to `/sales-manager/physical-allocation/kyc` with `customerContext` populated.</t>
+  </si>
+  <si>
+    <t>On webhook-confirmed payment, the unit becomes BOOKED, the registration becomes WINNER, and the SM is taken to the KYC screen with full customer context. WINNER status is permanent.</t>
+  </si>
+  <si>
+    <t>SM-FS §2.6 (System Actions), SM-WF §5 step 8, SM-WF §9 #5-6</t>
+  </si>
+  <si>
+    <t>`[STUB-EVIDENCE]` — confirmation screen requires non-destructive UAT payment path</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_FUNC_022</t>
+  </si>
+  <si>
+    <t>KYC — primary applicant fields pre-fill from registration</t>
+  </si>
+  <si>
+    <t>SM on `/kyc` with valid `customerContext.registration` from a successful checkout</t>
+  </si>
+  <si>
+    <t>1. Land on `/sales-manager/physical-allocation/kyc` after payment success. 2. Assert the primary applicant form is visible (currentStep = `applicants`). 3. Assert name, mobile, email, address fields are pre-populated with the customer's registration data.</t>
+  </si>
+  <si>
+    <t>Primary applicant section is auto-filled. SM can review and correct missing/incorrect fields but does not have to re-enter known data.</t>
+  </si>
+  <si>
+    <t>SM-FS §3.3 #1, SM-FS §3.6 #2, SM-FS §3.7 #1</t>
+  </si>
+  <si>
+    <t>`[STUB-EVIDENCE]` — requires customerContext (downstream of TC_021)</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_FUNC_023</t>
+  </si>
+  <si>
+    <t>KYC — all 4 documents required for primary applicant; partial upload blocks submit</t>
+  </si>
+  <si>
+    <t>SM on `/kyc` step 1</t>
+  </si>
+  <si>
+    <t>1. Leave PAN card unselected. 2. Upload Photo, Aadhaar front, Aadhaar back. 3. Click `Submit KYC`. 4. Assert submission is blocked and a field-level error or banner indicates the missing PAN.</t>
+  </si>
+  <si>
+    <t>All 4 documents (Photo, PAN, Aadhaar front, Aadhaar back) are mandatory. Submission must be blocked if any of the four is missing.</t>
+  </si>
+  <si>
+    <t>SM-FS §3.4, SM-FS §3.5, SM-FS §3.6 #3</t>
+  </si>
+  <si>
+    <t>`[STUB-EVIDENCE]` — KYC screen blocked by upstream context</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_FUNC_024</t>
+  </si>
+  <si>
+    <t>KYC — add co-applicants up to maximum 4 total; button hidden at limit</t>
+  </si>
+  <si>
+    <t>SM on `/kyc` with primary applicant filled</t>
+  </si>
+  <si>
+    <t>1. Click `+ Add Applicant` once → fill co-applicant #1. 2. Click again → fill co-applicant #2. 3. Click again → fill co-applicant #3 (now 4 applicants total). 4. Assert the `+ Add Applicant` button is no longer rendered (or disabled). 5. Assert label `Max. 4 Applicants allowed` is visible.</t>
+  </si>
+  <si>
+    <t>Maximum of 4 applicants is enforced (1 primary + 3 co-applicants). The Add Applicant control disappears or disables once the cap is reached and the cap label is shown.</t>
+  </si>
+  <si>
+    <t>SM-FS §3.3 #2, SM-FS §3.5, SM-BRD §4 #8</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_VAL_025</t>
+  </si>
+  <si>
+    <t>KYC — co-applicant relationship dropdown limited to blood relatives</t>
+  </si>
+  <si>
+    <t>SM on `/kyc`; co-applicant form open</t>
+  </si>
+  <si>
+    <t>1. Open the relationship dropdown for any co-applicant. 2. Read all options. 3. Assert the list is constrained to blood-relative roles (Father, Mother, Spouse, Son, Daughter, Sibling, etc.). 4. Assert no non-relative options (e.g. Friend, Colleague) are present.</t>
+  </si>
+  <si>
+    <t>Relationship dropdown enforces the blood-relative business rule by restricting selectable options.</t>
+  </si>
+  <si>
+    <t>SM-FS §3.5 (Relationship rule)</t>
+  </si>
+  <si>
+    <t>`[STUB-EVIDENCE]` — KYC blocked by upstream</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_FUNC_026</t>
+  </si>
+  <si>
+    <t>KYC submit — `POST /kyc/submit` payload schema</t>
+  </si>
+  <si>
+    <t>SM on `/kyc`; all required data filled</t>
+  </si>
+  <si>
+    <t>1. Fill primary applicant + at least one co-applicant; upload all 4 docs per applicant. 2. Click `Submit KYC`. 3. Capture the network call to `POST apiUrls.smPhysicalEvent.kyc.submit`. 4. Assert payload contains `userId`, `registrationUnitId`, `otpVerified`, `isParkingSelected: false`, `parkingCount: 0`.</t>
+  </si>
+  <si>
+    <t>KYC submission posts the documented payload schema. The server is the source of truth for `isKycSubmitted = true`.</t>
+  </si>
+  <si>
+    <t>SM-FS §3.6, SM-FS §3.7</t>
+  </si>
+  <si>
+    <t>`[STUB-EVIDENCE]` — requires full KYC context</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_E2E_027</t>
+  </si>
+  <si>
+    <t>KYC submit — `isKycSubmitted = true`, PDF generated, success screen</t>
+  </si>
+  <si>
+    <t>TC_026 submission accepted</t>
+  </si>
+  <si>
+    <t>1. After successful submit, observe response. 2. Verify `isKycSubmitted = true` is set on the registration unit (API or DB read). 3. Assert SM sees the confirmation/success step (`currentStep = 'success'` → `Completed` or `PaymentSuccess` component). 4. Confirm a KYC PDF was generated (Puppeteer artefact persisted to Azure Blob — verify via download URL in response if exposed).</t>
+  </si>
+  <si>
+    <t>The KYC unit record is marked submitted, a PDF is generated and stored, and the SM lands on the success state. Unit booking is now fully confirmed (no longer provisional).</t>
+  </si>
+  <si>
+    <t>SM-FS §3.6 #1, SM-FS §3.6 #5, SM-FS §3.7 #4</t>
+  </si>
+  <si>
+    <t>`[STUB-EVIDENCE]` — confirmation/success screen requires full live flow</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_BIZ_028</t>
+  </si>
+  <si>
+    <t>One allocation per registration — re-selecting a WINNER buyer should not allow another booking</t>
+  </si>
+  <si>
+    <t>SM logged in; a buyer registration in WINNER state for campaign 295 exists</t>
+  </si>
+  <si>
+    <t>1. Search the same buyer's phone whose registration is already WINNER. 2. Inspect the row — either it must not appear, or the Select button must be disabled / Action column must indicate "Already Allocated". 3. If Select is clickable, attempt the click and assert the system blocks further allocation.</t>
+  </si>
+  <si>
+    <t>A buyer with a WINNER registration cannot start a second allocation against the same campaign. The UI either hides the row or disables the action. (WINNER status is permanent — SM-WF §9 #6.)</t>
+  </si>
+  <si>
+    <t>SM-WF §9 #5, SM-WF §9 #6, SM-FS §1.5 #2</t>
+  </si>
+  <si>
+    <t>`[STUB-EVIDENCE]` — requires WINNER seed</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_BIZ_029</t>
+  </si>
+  <si>
+    <t>Only one allocation may proceed per customer at a time (single hold)</t>
+  </si>
+  <si>
+    <t>SM has an active HOLD on Unit A for Buyer X</t>
+  </si>
+  <si>
+    <t>1. With Unit A on HOLD for Buyer X, attempt to select Unit B for the same customer. 2. Assert system either disables Unit B selection or releases Unit A before holding Unit B (per FRD: only one held unit per customer).</t>
+  </si>
+  <si>
+    <t>The system enforces "only one unit can be held at a time per customer" (SM-FS §2.5 #3). Concurrent holds for the same customer are not allowed.</t>
+  </si>
+  <si>
+    <t>SM-FS §2.5 #3</t>
+  </si>
+  <si>
+    <t>`[STUB-EVIDENCE]` — requires customer context + multiple unit cells</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_NEG_030</t>
+  </si>
+  <si>
+    <t>Inactive campaign during session — search disabled mid-flight</t>
+  </si>
+  <si>
+    <t>SM was on landing during an active campaign; the campaign is then stopped/completed via Admin</t>
+  </si>
+  <si>
+    <t>1. Stay on `/sales-manager/physical-allocation` with search enabled. 2. From the Admin portal (or backend), stop the active campaign (status → STOPPED or COMPLETED). 3. Reload or wait for the next `/campaign/active` poll. 4. Assert the input + Scan QR button transition to `disabled=true` and the "No Active Campaign" card mounts.</t>
+  </si>
+  <si>
+    <t>When the active campaign ends, the SM's UI reflects this on next campaign-active fetch by disabling controls and showing the empty-state card.</t>
+  </si>
+  <si>
+    <t>SM-WF §4 (Campaign Status Flow), SM-BRD §4 #5</t>
+  </si>
+  <si>
+    <t>`allocation-loaded.png` (post-state), `allocation-loaded-active.png` (pre-state)</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_API_031</t>
+  </si>
+  <si>
+    <t>Active campaign API — response shape and required fields</t>
+  </si>
+  <si>
+    <t>SM session token valid</t>
+  </si>
+  <si>
+    <t>1. Call `GET https://uat-api.xrportal.in/api/v1/sales-manager/physical-event/campaign/active` with SM session. 2. Assert HTTP 200. 3. Assert payload contains `id`, `name`, `status`, `startTime`, `endTime`. 4. When a campaign is RUNNING, assert `status === 'RUNNING'`.</t>
+  </si>
+  <si>
+    <t>Active-campaign endpoint returns the documented schema. When `status === 'RUNNING'`, the SM UI enables search and Scan QR.</t>
+  </si>
+  <si>
+    <t>SM-FS §1.6, SM-WF §4</t>
+  </si>
+  <si>
+    <t>`allocation-loaded-active.png` (UI cue)</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_API_032</t>
+  </si>
+  <si>
+    <t>Customer search API — campaignId scoping enforced server-side</t>
+  </si>
+  <si>
+    <t>SM session; active campaign 295</t>
+  </si>
+  <si>
+    <t>1. Call `GET /api/v1/sales-manager/physical-event/search?campaignId=295&amp;q=8888888888`. 2. Assert HTTP 200. 3. Assert `data` is an array. 4. Repeat with `campaignId=&lt;another id&gt;` and assert results are scoped to that campaign id only.</t>
+  </si>
+  <si>
+    <t>The search endpoint scopes results strictly by `campaignId`. Cross-campaign data does not leak.</t>
+  </si>
+  <si>
+    <t>SM-FS §1.6 #1, SM-WF §9 (one active campaign at a time)</t>
+  </si>
+  <si>
+    <t>`allocation-search-result.png` (UI consumer)</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_UI_033</t>
+  </si>
+  <si>
+    <t>Sidebar — three nav items and Logout button</t>
+  </si>
+  <si>
+    <t>1. Inspect the SM Portal sidebar. 2. Assert exactly three nav items: `Callback Requests`, `Towers`, `Allocation`. 3. Assert a `Logout` button at the foot.</t>
+  </si>
+  <si>
+    <t>Sidebar renders three nav items plus Logout. The Allocation icon is a calendar glyph.</t>
+  </si>
+  <si>
+    <t>SM-BRD §3, INDEX.md "Sidebar"</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_REG_034</t>
+  </si>
+  <si>
+    <t>Regression — global header strip is static and not campaign-driven</t>
+  </si>
+  <si>
+    <t>SM logged in; any campaign state</t>
+  </si>
+  <si>
+    <t>1. Compare the top header strip across active and inactive campaign states. 2. Assert it always reads `India's Biggest Growth Housing Revolution Begins On 7th April 2026.` regardless of `/campaign/active` response.</t>
+  </si>
+  <si>
+    <t>The marketing strip is global chrome and does not change with campaign status. Tests must not rely on it as a campaign-active signal.</t>
+  </si>
+  <si>
+    <t>INDEX.md "Active Campaign" note</t>
+  </si>
+  <si>
+    <t>`allocation-loaded-active.png`, `allocation-loaded.png`</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_EDGE_035</t>
+  </si>
+  <si>
+    <t>Debounce — rapid typing collapses to a single API call</t>
+  </si>
+  <si>
+    <t>1. Type `8888888888` in rapid succession (under 500 ms between keystrokes). 2. After typing stops, wait 1 s. 3. Assert exactly one `GET /search?...q=8888888888` request fired (not one per keystroke).</t>
+  </si>
+  <si>
+    <t>The 500 ms debounce collapses fast typing into a single API call with the final query.</t>
+  </si>
+  <si>
+    <t>SM-FS §1.6, INDEX.md "Debounce"</t>
   </si>
   <si>
     <t>Total TCs</t>
@@ -15400,7 +17035,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P958"/>
+  <dimension ref="A1:P1048"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -63018,6 +64653,4506 @@
       </c>
       <c r="P958" t="s">
         <v>4694</v>
+      </c>
+    </row>
+    <row r="959" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A959" t="s">
+        <v>4695</v>
+      </c>
+      <c r="B959" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C959" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D959" t="s">
+        <v>30</v>
+      </c>
+      <c r="E959" t="s">
+        <v>4696</v>
+      </c>
+      <c r="F959" t="s">
+        <v>33</v>
+      </c>
+      <c r="G959" t="s">
+        <v>4697</v>
+      </c>
+      <c r="H959" t="s">
+        <v>4698</v>
+      </c>
+      <c r="I959" t="s">
+        <v>4699</v>
+      </c>
+      <c r="J959" t="s">
+        <v>26</v>
+      </c>
+      <c r="K959" t="s">
+        <v>4700</v>
+      </c>
+      <c r="L959" t="s">
+        <v>30</v>
+      </c>
+      <c r="M959" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N959" t="s">
+        <v>30</v>
+      </c>
+      <c r="O959" t="s">
+        <v>30</v>
+      </c>
+      <c r="P959" t="s">
+        <v>4701</v>
+      </c>
+    </row>
+    <row r="960" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A960" t="s">
+        <v>4702</v>
+      </c>
+      <c r="B960" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C960" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D960" t="s">
+        <v>30</v>
+      </c>
+      <c r="E960" t="s">
+        <v>4703</v>
+      </c>
+      <c r="F960" t="s">
+        <v>48</v>
+      </c>
+      <c r="G960" t="s">
+        <v>4704</v>
+      </c>
+      <c r="H960" t="s">
+        <v>4705</v>
+      </c>
+      <c r="I960" t="s">
+        <v>4706</v>
+      </c>
+      <c r="J960" t="s">
+        <v>26</v>
+      </c>
+      <c r="K960" t="s">
+        <v>4707</v>
+      </c>
+      <c r="L960" t="s">
+        <v>30</v>
+      </c>
+      <c r="M960" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N960" t="s">
+        <v>30</v>
+      </c>
+      <c r="O960" t="s">
+        <v>30</v>
+      </c>
+      <c r="P960" t="s">
+        <v>4701</v>
+      </c>
+    </row>
+    <row r="961" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A961" t="s">
+        <v>4708</v>
+      </c>
+      <c r="B961" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C961" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D961" t="s">
+        <v>30</v>
+      </c>
+      <c r="E961" t="s">
+        <v>4709</v>
+      </c>
+      <c r="F961" t="s">
+        <v>48</v>
+      </c>
+      <c r="G961" t="s">
+        <v>4207</v>
+      </c>
+      <c r="H961" t="s">
+        <v>4710</v>
+      </c>
+      <c r="I961" t="s">
+        <v>4711</v>
+      </c>
+      <c r="J961" t="s">
+        <v>26</v>
+      </c>
+      <c r="K961" t="s">
+        <v>4712</v>
+      </c>
+      <c r="L961" t="s">
+        <v>30</v>
+      </c>
+      <c r="M961" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N961" t="s">
+        <v>30</v>
+      </c>
+      <c r="O961" t="s">
+        <v>30</v>
+      </c>
+      <c r="P961" t="s">
+        <v>4701</v>
+      </c>
+    </row>
+    <row r="962" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A962" t="s">
+        <v>4713</v>
+      </c>
+      <c r="B962" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C962" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D962" t="s">
+        <v>30</v>
+      </c>
+      <c r="E962" t="s">
+        <v>4714</v>
+      </c>
+      <c r="F962" t="s">
+        <v>172</v>
+      </c>
+      <c r="G962" t="s">
+        <v>4715</v>
+      </c>
+      <c r="H962" t="s">
+        <v>4716</v>
+      </c>
+      <c r="I962" t="s">
+        <v>4717</v>
+      </c>
+      <c r="J962" t="s">
+        <v>26</v>
+      </c>
+      <c r="K962" t="s">
+        <v>4712</v>
+      </c>
+      <c r="L962" t="s">
+        <v>30</v>
+      </c>
+      <c r="M962" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N962" t="s">
+        <v>30</v>
+      </c>
+      <c r="O962" t="s">
+        <v>30</v>
+      </c>
+      <c r="P962" t="s">
+        <v>4701</v>
+      </c>
+    </row>
+    <row r="963" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A963" t="s">
+        <v>4718</v>
+      </c>
+      <c r="B963" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C963" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D963" t="s">
+        <v>30</v>
+      </c>
+      <c r="E963" t="s">
+        <v>4719</v>
+      </c>
+      <c r="F963" t="s">
+        <v>33</v>
+      </c>
+      <c r="G963" t="s">
+        <v>4720</v>
+      </c>
+      <c r="H963" t="s">
+        <v>4721</v>
+      </c>
+      <c r="I963" t="s">
+        <v>4722</v>
+      </c>
+      <c r="J963" t="s">
+        <v>26</v>
+      </c>
+      <c r="K963" t="s">
+        <v>4723</v>
+      </c>
+      <c r="L963" t="s">
+        <v>30</v>
+      </c>
+      <c r="M963" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N963" t="s">
+        <v>30</v>
+      </c>
+      <c r="O963" t="s">
+        <v>30</v>
+      </c>
+      <c r="P963" t="s">
+        <v>4724</v>
+      </c>
+    </row>
+    <row r="964" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A964" t="s">
+        <v>4725</v>
+      </c>
+      <c r="B964" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C964" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D964" t="s">
+        <v>30</v>
+      </c>
+      <c r="E964" t="s">
+        <v>4726</v>
+      </c>
+      <c r="F964" t="s">
+        <v>33</v>
+      </c>
+      <c r="G964" t="s">
+        <v>4727</v>
+      </c>
+      <c r="H964" t="s">
+        <v>4728</v>
+      </c>
+      <c r="I964" t="s">
+        <v>4729</v>
+      </c>
+      <c r="J964" t="s">
+        <v>26</v>
+      </c>
+      <c r="K964" t="s">
+        <v>4730</v>
+      </c>
+      <c r="L964" t="s">
+        <v>30</v>
+      </c>
+      <c r="M964" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N964" t="s">
+        <v>30</v>
+      </c>
+      <c r="O964" t="s">
+        <v>30</v>
+      </c>
+      <c r="P964" t="s">
+        <v>4724</v>
+      </c>
+    </row>
+    <row r="965" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A965" t="s">
+        <v>4731</v>
+      </c>
+      <c r="B965" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C965" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D965" t="s">
+        <v>30</v>
+      </c>
+      <c r="E965" t="s">
+        <v>4732</v>
+      </c>
+      <c r="F965" t="s">
+        <v>33</v>
+      </c>
+      <c r="G965" t="s">
+        <v>4733</v>
+      </c>
+      <c r="H965" t="s">
+        <v>4734</v>
+      </c>
+      <c r="I965" t="s">
+        <v>4735</v>
+      </c>
+      <c r="J965" t="s">
+        <v>26</v>
+      </c>
+      <c r="K965" t="s">
+        <v>4736</v>
+      </c>
+      <c r="L965" t="s">
+        <v>30</v>
+      </c>
+      <c r="M965" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N965" t="s">
+        <v>30</v>
+      </c>
+      <c r="O965" t="s">
+        <v>30</v>
+      </c>
+      <c r="P965" t="s">
+        <v>4724</v>
+      </c>
+    </row>
+    <row r="966" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A966" t="s">
+        <v>4737</v>
+      </c>
+      <c r="B966" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C966" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D966" t="s">
+        <v>30</v>
+      </c>
+      <c r="E966" t="s">
+        <v>4738</v>
+      </c>
+      <c r="F966" t="s">
+        <v>33</v>
+      </c>
+      <c r="G966" t="s">
+        <v>4739</v>
+      </c>
+      <c r="H966" t="s">
+        <v>4740</v>
+      </c>
+      <c r="I966" t="s">
+        <v>4741</v>
+      </c>
+      <c r="J966" t="s">
+        <v>26</v>
+      </c>
+      <c r="K966" t="s">
+        <v>4742</v>
+      </c>
+      <c r="L966" t="s">
+        <v>30</v>
+      </c>
+      <c r="M966" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N966" t="s">
+        <v>30</v>
+      </c>
+      <c r="O966" t="s">
+        <v>30</v>
+      </c>
+      <c r="P966" t="s">
+        <v>4743</v>
+      </c>
+    </row>
+    <row r="967" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A967" t="s">
+        <v>4744</v>
+      </c>
+      <c r="B967" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C967" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D967" t="s">
+        <v>30</v>
+      </c>
+      <c r="E967" t="s">
+        <v>4745</v>
+      </c>
+      <c r="F967" t="s">
+        <v>33</v>
+      </c>
+      <c r="G967" t="s">
+        <v>4715</v>
+      </c>
+      <c r="H967" t="s">
+        <v>4746</v>
+      </c>
+      <c r="I967" t="s">
+        <v>4747</v>
+      </c>
+      <c r="J967" t="s">
+        <v>26</v>
+      </c>
+      <c r="K967" t="s">
+        <v>4730</v>
+      </c>
+      <c r="L967" t="s">
+        <v>30</v>
+      </c>
+      <c r="M967" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N967" t="s">
+        <v>30</v>
+      </c>
+      <c r="O967" t="s">
+        <v>30</v>
+      </c>
+      <c r="P967" t="s">
+        <v>4748</v>
+      </c>
+    </row>
+    <row r="968" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A968" t="s">
+        <v>4749</v>
+      </c>
+      <c r="B968" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C968" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D968" t="s">
+        <v>30</v>
+      </c>
+      <c r="E968" t="s">
+        <v>4750</v>
+      </c>
+      <c r="F968" t="s">
+        <v>33</v>
+      </c>
+      <c r="G968" t="s">
+        <v>4751</v>
+      </c>
+      <c r="H968" t="s">
+        <v>4752</v>
+      </c>
+      <c r="I968" t="s">
+        <v>4753</v>
+      </c>
+      <c r="J968" t="s">
+        <v>26</v>
+      </c>
+      <c r="K968" t="s">
+        <v>4730</v>
+      </c>
+      <c r="L968" t="s">
+        <v>30</v>
+      </c>
+      <c r="M968" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N968" t="s">
+        <v>30</v>
+      </c>
+      <c r="O968" t="s">
+        <v>30</v>
+      </c>
+      <c r="P968" t="s">
+        <v>4748</v>
+      </c>
+    </row>
+    <row r="969" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A969" t="s">
+        <v>4754</v>
+      </c>
+      <c r="B969" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C969" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D969" t="s">
+        <v>30</v>
+      </c>
+      <c r="E969" t="s">
+        <v>4755</v>
+      </c>
+      <c r="F969" t="s">
+        <v>48</v>
+      </c>
+      <c r="G969" t="s">
+        <v>4715</v>
+      </c>
+      <c r="H969" t="s">
+        <v>4756</v>
+      </c>
+      <c r="I969" t="s">
+        <v>4757</v>
+      </c>
+      <c r="J969" t="s">
+        <v>26</v>
+      </c>
+      <c r="K969" t="s">
+        <v>4758</v>
+      </c>
+      <c r="L969" t="s">
+        <v>30</v>
+      </c>
+      <c r="M969" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N969" t="s">
+        <v>30</v>
+      </c>
+      <c r="O969" t="s">
+        <v>30</v>
+      </c>
+      <c r="P969" t="s">
+        <v>4724</v>
+      </c>
+    </row>
+    <row r="970" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A970" t="s">
+        <v>4759</v>
+      </c>
+      <c r="B970" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C970" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D970" t="s">
+        <v>30</v>
+      </c>
+      <c r="E970" t="s">
+        <v>4760</v>
+      </c>
+      <c r="F970" t="s">
+        <v>33</v>
+      </c>
+      <c r="G970" t="s">
+        <v>4715</v>
+      </c>
+      <c r="H970" t="s">
+        <v>4761</v>
+      </c>
+      <c r="I970" t="s">
+        <v>4762</v>
+      </c>
+      <c r="J970" t="s">
+        <v>26</v>
+      </c>
+      <c r="K970" t="s">
+        <v>4763</v>
+      </c>
+      <c r="L970" t="s">
+        <v>30</v>
+      </c>
+      <c r="M970" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N970" t="s">
+        <v>30</v>
+      </c>
+      <c r="O970" t="s">
+        <v>30</v>
+      </c>
+      <c r="P970" t="s">
+        <v>4701</v>
+      </c>
+    </row>
+    <row r="971" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A971" t="s">
+        <v>4764</v>
+      </c>
+      <c r="B971" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C971" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D971" t="s">
+        <v>30</v>
+      </c>
+      <c r="E971" t="s">
+        <v>4765</v>
+      </c>
+      <c r="F971" t="s">
+        <v>33</v>
+      </c>
+      <c r="G971" t="s">
+        <v>4766</v>
+      </c>
+      <c r="H971" t="s">
+        <v>4767</v>
+      </c>
+      <c r="I971" t="s">
+        <v>4768</v>
+      </c>
+      <c r="J971" t="s">
+        <v>26</v>
+      </c>
+      <c r="K971" t="s">
+        <v>4723</v>
+      </c>
+      <c r="L971" t="s">
+        <v>30</v>
+      </c>
+      <c r="M971" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N971" t="s">
+        <v>30</v>
+      </c>
+      <c r="O971" t="s">
+        <v>30</v>
+      </c>
+      <c r="P971" t="s">
+        <v>4701</v>
+      </c>
+    </row>
+    <row r="972" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A972" t="s">
+        <v>4769</v>
+      </c>
+      <c r="B972" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C972" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D972" t="s">
+        <v>30</v>
+      </c>
+      <c r="E972" t="s">
+        <v>4770</v>
+      </c>
+      <c r="F972" t="s">
+        <v>33</v>
+      </c>
+      <c r="G972" t="s">
+        <v>4715</v>
+      </c>
+      <c r="H972" t="s">
+        <v>4771</v>
+      </c>
+      <c r="I972" t="s">
+        <v>4772</v>
+      </c>
+      <c r="J972" t="s">
+        <v>26</v>
+      </c>
+      <c r="K972" t="s">
+        <v>4723</v>
+      </c>
+      <c r="L972" t="s">
+        <v>30</v>
+      </c>
+      <c r="M972" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N972" t="s">
+        <v>30</v>
+      </c>
+      <c r="O972" t="s">
+        <v>30</v>
+      </c>
+      <c r="P972" t="s">
+        <v>4773</v>
+      </c>
+    </row>
+    <row r="973" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A973" t="s">
+        <v>4774</v>
+      </c>
+      <c r="B973" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C973" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D973" t="s">
+        <v>30</v>
+      </c>
+      <c r="E973" t="s">
+        <v>4775</v>
+      </c>
+      <c r="F973" t="s">
+        <v>48</v>
+      </c>
+      <c r="G973" t="s">
+        <v>4776</v>
+      </c>
+      <c r="H973" t="s">
+        <v>4777</v>
+      </c>
+      <c r="I973" t="s">
+        <v>4778</v>
+      </c>
+      <c r="J973" t="s">
+        <v>26</v>
+      </c>
+      <c r="K973" t="s">
+        <v>4723</v>
+      </c>
+      <c r="L973" t="s">
+        <v>30</v>
+      </c>
+      <c r="M973" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N973" t="s">
+        <v>30</v>
+      </c>
+      <c r="O973" t="s">
+        <v>30</v>
+      </c>
+      <c r="P973" t="s">
+        <v>4701</v>
+      </c>
+    </row>
+    <row r="974" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A974" t="s">
+        <v>4779</v>
+      </c>
+      <c r="B974" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C974" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D974" t="s">
+        <v>30</v>
+      </c>
+      <c r="E974" t="s">
+        <v>4780</v>
+      </c>
+      <c r="F974" t="s">
+        <v>48</v>
+      </c>
+      <c r="G974" t="s">
+        <v>4715</v>
+      </c>
+      <c r="H974" t="s">
+        <v>4781</v>
+      </c>
+      <c r="I974" t="s">
+        <v>4782</v>
+      </c>
+      <c r="J974" t="s">
+        <v>26</v>
+      </c>
+      <c r="K974" t="s">
+        <v>4783</v>
+      </c>
+      <c r="L974" t="s">
+        <v>30</v>
+      </c>
+      <c r="M974" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N974" t="s">
+        <v>30</v>
+      </c>
+      <c r="O974" t="s">
+        <v>30</v>
+      </c>
+      <c r="P974" t="s">
+        <v>4701</v>
+      </c>
+    </row>
+    <row r="975" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A975" t="s">
+        <v>4784</v>
+      </c>
+      <c r="B975" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C975" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D975" t="s">
+        <v>30</v>
+      </c>
+      <c r="E975" t="s">
+        <v>4785</v>
+      </c>
+      <c r="F975" t="s">
+        <v>48</v>
+      </c>
+      <c r="G975" t="s">
+        <v>4715</v>
+      </c>
+      <c r="H975" t="s">
+        <v>4786</v>
+      </c>
+      <c r="I975" t="s">
+        <v>4787</v>
+      </c>
+      <c r="J975" t="s">
+        <v>26</v>
+      </c>
+      <c r="K975" t="s">
+        <v>4788</v>
+      </c>
+      <c r="L975" t="s">
+        <v>30</v>
+      </c>
+      <c r="M975" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N975" t="s">
+        <v>30</v>
+      </c>
+      <c r="O975" t="s">
+        <v>30</v>
+      </c>
+      <c r="P975" t="s">
+        <v>4701</v>
+      </c>
+    </row>
+    <row r="976" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A976" t="s">
+        <v>4789</v>
+      </c>
+      <c r="B976" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C976" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D976" t="s">
+        <v>30</v>
+      </c>
+      <c r="E976" t="s">
+        <v>4790</v>
+      </c>
+      <c r="F976" t="s">
+        <v>48</v>
+      </c>
+      <c r="G976" t="s">
+        <v>4791</v>
+      </c>
+      <c r="H976" t="s">
+        <v>4792</v>
+      </c>
+      <c r="I976" t="s">
+        <v>4793</v>
+      </c>
+      <c r="J976" t="s">
+        <v>26</v>
+      </c>
+      <c r="K976" t="s">
+        <v>4794</v>
+      </c>
+      <c r="L976" t="s">
+        <v>30</v>
+      </c>
+      <c r="M976" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N976" t="s">
+        <v>30</v>
+      </c>
+      <c r="O976" t="s">
+        <v>30</v>
+      </c>
+      <c r="P976" t="s">
+        <v>4701</v>
+      </c>
+    </row>
+    <row r="977" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A977" t="s">
+        <v>4795</v>
+      </c>
+      <c r="B977" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C977" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D977" t="s">
+        <v>30</v>
+      </c>
+      <c r="E977" t="s">
+        <v>4796</v>
+      </c>
+      <c r="F977" t="s">
+        <v>33</v>
+      </c>
+      <c r="G977" t="s">
+        <v>4797</v>
+      </c>
+      <c r="H977" t="s">
+        <v>4798</v>
+      </c>
+      <c r="I977" t="s">
+        <v>4799</v>
+      </c>
+      <c r="J977" t="s">
+        <v>26</v>
+      </c>
+      <c r="K977" t="s">
+        <v>4800</v>
+      </c>
+      <c r="L977" t="s">
+        <v>30</v>
+      </c>
+      <c r="M977" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N977" t="s">
+        <v>30</v>
+      </c>
+      <c r="O977" t="s">
+        <v>30</v>
+      </c>
+      <c r="P977" t="s">
+        <v>4801</v>
+      </c>
+    </row>
+    <row r="978" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A978" t="s">
+        <v>4802</v>
+      </c>
+      <c r="B978" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C978" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D978" t="s">
+        <v>30</v>
+      </c>
+      <c r="E978" t="s">
+        <v>4803</v>
+      </c>
+      <c r="F978" t="s">
+        <v>33</v>
+      </c>
+      <c r="G978" t="s">
+        <v>4804</v>
+      </c>
+      <c r="H978" t="s">
+        <v>4805</v>
+      </c>
+      <c r="I978" t="s">
+        <v>4806</v>
+      </c>
+      <c r="J978" t="s">
+        <v>26</v>
+      </c>
+      <c r="K978" t="s">
+        <v>4807</v>
+      </c>
+      <c r="L978" t="s">
+        <v>30</v>
+      </c>
+      <c r="M978" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N978" t="s">
+        <v>30</v>
+      </c>
+      <c r="O978" t="s">
+        <v>30</v>
+      </c>
+      <c r="P978" t="s">
+        <v>4801</v>
+      </c>
+    </row>
+    <row r="979" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A979" t="s">
+        <v>4808</v>
+      </c>
+      <c r="B979" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C979" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D979" t="s">
+        <v>30</v>
+      </c>
+      <c r="E979" t="s">
+        <v>4809</v>
+      </c>
+      <c r="F979" t="s">
+        <v>48</v>
+      </c>
+      <c r="G979" t="s">
+        <v>4810</v>
+      </c>
+      <c r="H979" t="s">
+        <v>4811</v>
+      </c>
+      <c r="I979" t="s">
+        <v>4812</v>
+      </c>
+      <c r="J979" t="s">
+        <v>26</v>
+      </c>
+      <c r="K979" t="s">
+        <v>4813</v>
+      </c>
+      <c r="L979" t="s">
+        <v>30</v>
+      </c>
+      <c r="M979" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N979" t="s">
+        <v>30</v>
+      </c>
+      <c r="O979" t="s">
+        <v>30</v>
+      </c>
+      <c r="P979" t="s">
+        <v>4814</v>
+      </c>
+    </row>
+    <row r="980" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A980" t="s">
+        <v>4815</v>
+      </c>
+      <c r="B980" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C980" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D980" t="s">
+        <v>30</v>
+      </c>
+      <c r="E980" t="s">
+        <v>4816</v>
+      </c>
+      <c r="F980" t="s">
+        <v>33</v>
+      </c>
+      <c r="G980" t="s">
+        <v>4817</v>
+      </c>
+      <c r="H980" t="s">
+        <v>4818</v>
+      </c>
+      <c r="I980" t="s">
+        <v>4819</v>
+      </c>
+      <c r="J980" t="s">
+        <v>26</v>
+      </c>
+      <c r="K980" t="s">
+        <v>4820</v>
+      </c>
+      <c r="L980" t="s">
+        <v>30</v>
+      </c>
+      <c r="M980" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N980" t="s">
+        <v>30</v>
+      </c>
+      <c r="O980" t="s">
+        <v>30</v>
+      </c>
+      <c r="P980" t="s">
+        <v>4821</v>
+      </c>
+    </row>
+    <row r="981" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A981" t="s">
+        <v>4822</v>
+      </c>
+      <c r="B981" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C981" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D981" t="s">
+        <v>30</v>
+      </c>
+      <c r="E981" t="s">
+        <v>4823</v>
+      </c>
+      <c r="F981" t="s">
+        <v>33</v>
+      </c>
+      <c r="G981" t="s">
+        <v>4824</v>
+      </c>
+      <c r="H981" t="s">
+        <v>4825</v>
+      </c>
+      <c r="I981" t="s">
+        <v>4826</v>
+      </c>
+      <c r="J981" t="s">
+        <v>26</v>
+      </c>
+      <c r="K981" t="s">
+        <v>4827</v>
+      </c>
+      <c r="L981" t="s">
+        <v>30</v>
+      </c>
+      <c r="M981" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N981" t="s">
+        <v>30</v>
+      </c>
+      <c r="O981" t="s">
+        <v>30</v>
+      </c>
+      <c r="P981" t="s">
+        <v>4828</v>
+      </c>
+    </row>
+    <row r="982" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A982" t="s">
+        <v>4829</v>
+      </c>
+      <c r="B982" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C982" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D982" t="s">
+        <v>30</v>
+      </c>
+      <c r="E982" t="s">
+        <v>4830</v>
+      </c>
+      <c r="F982" t="s">
+        <v>48</v>
+      </c>
+      <c r="G982" t="s">
+        <v>441</v>
+      </c>
+      <c r="H982" t="s">
+        <v>4831</v>
+      </c>
+      <c r="I982" t="s">
+        <v>4832</v>
+      </c>
+      <c r="J982" t="s">
+        <v>26</v>
+      </c>
+      <c r="K982" t="s">
+        <v>4723</v>
+      </c>
+      <c r="L982" t="s">
+        <v>30</v>
+      </c>
+      <c r="M982" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N982" t="s">
+        <v>30</v>
+      </c>
+      <c r="O982" t="s">
+        <v>30</v>
+      </c>
+      <c r="P982" t="s">
+        <v>4801</v>
+      </c>
+    </row>
+    <row r="983" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A983" t="s">
+        <v>4833</v>
+      </c>
+      <c r="B983" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C983" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D983" t="s">
+        <v>30</v>
+      </c>
+      <c r="E983" t="s">
+        <v>4834</v>
+      </c>
+      <c r="F983" t="s">
+        <v>33</v>
+      </c>
+      <c r="G983" t="s">
+        <v>4804</v>
+      </c>
+      <c r="H983" t="s">
+        <v>4835</v>
+      </c>
+      <c r="I983" t="s">
+        <v>4836</v>
+      </c>
+      <c r="J983" t="s">
+        <v>26</v>
+      </c>
+      <c r="K983" t="s">
+        <v>4837</v>
+      </c>
+      <c r="L983" t="s">
+        <v>30</v>
+      </c>
+      <c r="M983" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N983" t="s">
+        <v>30</v>
+      </c>
+      <c r="O983" t="s">
+        <v>30</v>
+      </c>
+      <c r="P983" t="s">
+        <v>4838</v>
+      </c>
+    </row>
+    <row r="984" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A984" t="s">
+        <v>4839</v>
+      </c>
+      <c r="B984" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C984" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D984" t="s">
+        <v>30</v>
+      </c>
+      <c r="E984" t="s">
+        <v>4840</v>
+      </c>
+      <c r="F984" t="s">
+        <v>33</v>
+      </c>
+      <c r="G984" t="s">
+        <v>4810</v>
+      </c>
+      <c r="H984" t="s">
+        <v>4841</v>
+      </c>
+      <c r="I984" t="s">
+        <v>4842</v>
+      </c>
+      <c r="J984" t="s">
+        <v>26</v>
+      </c>
+      <c r="K984" t="s">
+        <v>4843</v>
+      </c>
+      <c r="L984" t="s">
+        <v>30</v>
+      </c>
+      <c r="M984" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N984" t="s">
+        <v>30</v>
+      </c>
+      <c r="O984" t="s">
+        <v>30</v>
+      </c>
+      <c r="P984" t="s">
+        <v>4844</v>
+      </c>
+    </row>
+    <row r="985" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A985" t="s">
+        <v>4845</v>
+      </c>
+      <c r="B985" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C985" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D985" t="s">
+        <v>30</v>
+      </c>
+      <c r="E985" t="s">
+        <v>4846</v>
+      </c>
+      <c r="F985" t="s">
+        <v>33</v>
+      </c>
+      <c r="G985" t="s">
+        <v>4847</v>
+      </c>
+      <c r="H985" t="s">
+        <v>4848</v>
+      </c>
+      <c r="I985" t="s">
+        <v>4849</v>
+      </c>
+      <c r="J985" t="s">
+        <v>26</v>
+      </c>
+      <c r="K985" t="s">
+        <v>4850</v>
+      </c>
+      <c r="L985" t="s">
+        <v>30</v>
+      </c>
+      <c r="M985" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N985" t="s">
+        <v>30</v>
+      </c>
+      <c r="O985" t="s">
+        <v>30</v>
+      </c>
+      <c r="P985" t="s">
+        <v>4851</v>
+      </c>
+    </row>
+    <row r="986" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A986" t="s">
+        <v>4852</v>
+      </c>
+      <c r="B986" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C986" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D986" t="s">
+        <v>30</v>
+      </c>
+      <c r="E986" t="s">
+        <v>4853</v>
+      </c>
+      <c r="F986" t="s">
+        <v>48</v>
+      </c>
+      <c r="G986" t="s">
+        <v>4854</v>
+      </c>
+      <c r="H986" t="s">
+        <v>4855</v>
+      </c>
+      <c r="I986" t="s">
+        <v>4856</v>
+      </c>
+      <c r="J986" t="s">
+        <v>26</v>
+      </c>
+      <c r="K986" t="s">
+        <v>4857</v>
+      </c>
+      <c r="L986" t="s">
+        <v>30</v>
+      </c>
+      <c r="M986" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N986" t="s">
+        <v>30</v>
+      </c>
+      <c r="O986" t="s">
+        <v>30</v>
+      </c>
+      <c r="P986" t="s">
+        <v>4858</v>
+      </c>
+    </row>
+    <row r="987" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A987" t="s">
+        <v>4859</v>
+      </c>
+      <c r="B987" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C987" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D987" t="s">
+        <v>30</v>
+      </c>
+      <c r="E987" t="s">
+        <v>4860</v>
+      </c>
+      <c r="F987" t="s">
+        <v>33</v>
+      </c>
+      <c r="G987" t="s">
+        <v>4861</v>
+      </c>
+      <c r="H987" t="s">
+        <v>4862</v>
+      </c>
+      <c r="I987" t="s">
+        <v>4863</v>
+      </c>
+      <c r="J987" t="s">
+        <v>26</v>
+      </c>
+      <c r="K987" t="s">
+        <v>4864</v>
+      </c>
+      <c r="L987" t="s">
+        <v>30</v>
+      </c>
+      <c r="M987" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N987" t="s">
+        <v>30</v>
+      </c>
+      <c r="O987" t="s">
+        <v>30</v>
+      </c>
+      <c r="P987" t="s">
+        <v>4865</v>
+      </c>
+    </row>
+    <row r="988" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A988" t="s">
+        <v>4866</v>
+      </c>
+      <c r="B988" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C988" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D988" t="s">
+        <v>30</v>
+      </c>
+      <c r="E988" t="s">
+        <v>4867</v>
+      </c>
+      <c r="F988" t="s">
+        <v>33</v>
+      </c>
+      <c r="G988" t="s">
+        <v>4868</v>
+      </c>
+      <c r="H988" t="s">
+        <v>4869</v>
+      </c>
+      <c r="I988" t="s">
+        <v>4870</v>
+      </c>
+      <c r="J988" t="s">
+        <v>26</v>
+      </c>
+      <c r="K988" t="s">
+        <v>4871</v>
+      </c>
+      <c r="L988" t="s">
+        <v>30</v>
+      </c>
+      <c r="M988" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N988" t="s">
+        <v>30</v>
+      </c>
+      <c r="O988" t="s">
+        <v>30</v>
+      </c>
+      <c r="P988" t="s">
+        <v>4872</v>
+      </c>
+    </row>
+    <row r="989" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A989" t="s">
+        <v>4873</v>
+      </c>
+      <c r="B989" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C989" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D989" t="s">
+        <v>30</v>
+      </c>
+      <c r="E989" t="s">
+        <v>4874</v>
+      </c>
+      <c r="F989" t="s">
+        <v>33</v>
+      </c>
+      <c r="G989" t="s">
+        <v>483</v>
+      </c>
+      <c r="H989" t="s">
+        <v>4875</v>
+      </c>
+      <c r="I989" t="s">
+        <v>4876</v>
+      </c>
+      <c r="J989" t="s">
+        <v>26</v>
+      </c>
+      <c r="K989" t="s">
+        <v>4871</v>
+      </c>
+      <c r="L989" t="s">
+        <v>30</v>
+      </c>
+      <c r="M989" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N989" t="s">
+        <v>30</v>
+      </c>
+      <c r="O989" t="s">
+        <v>30</v>
+      </c>
+      <c r="P989" t="s">
+        <v>4865</v>
+      </c>
+    </row>
+    <row r="990" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A990" t="s">
+        <v>4877</v>
+      </c>
+      <c r="B990" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C990" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D990" t="s">
+        <v>30</v>
+      </c>
+      <c r="E990" t="s">
+        <v>4878</v>
+      </c>
+      <c r="F990" t="s">
+        <v>33</v>
+      </c>
+      <c r="G990" t="s">
+        <v>4879</v>
+      </c>
+      <c r="H990" t="s">
+        <v>4880</v>
+      </c>
+      <c r="I990" t="s">
+        <v>4881</v>
+      </c>
+      <c r="J990" t="s">
+        <v>26</v>
+      </c>
+      <c r="K990" t="s">
+        <v>4882</v>
+      </c>
+      <c r="L990" t="s">
+        <v>30</v>
+      </c>
+      <c r="M990" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N990" t="s">
+        <v>30</v>
+      </c>
+      <c r="O990" t="s">
+        <v>30</v>
+      </c>
+      <c r="P990" t="s">
+        <v>4865</v>
+      </c>
+    </row>
+    <row r="991" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A991" t="s">
+        <v>4883</v>
+      </c>
+      <c r="B991" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C991" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D991" t="s">
+        <v>30</v>
+      </c>
+      <c r="E991" t="s">
+        <v>4884</v>
+      </c>
+      <c r="F991" t="s">
+        <v>33</v>
+      </c>
+      <c r="G991" t="s">
+        <v>4885</v>
+      </c>
+      <c r="H991" t="s">
+        <v>4886</v>
+      </c>
+      <c r="I991" t="s">
+        <v>4887</v>
+      </c>
+      <c r="J991" t="s">
+        <v>26</v>
+      </c>
+      <c r="K991" t="s">
+        <v>4888</v>
+      </c>
+      <c r="L991" t="s">
+        <v>30</v>
+      </c>
+      <c r="M991" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N991" t="s">
+        <v>30</v>
+      </c>
+      <c r="O991" t="s">
+        <v>30</v>
+      </c>
+      <c r="P991" t="s">
+        <v>4865</v>
+      </c>
+    </row>
+    <row r="992" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A992" t="s">
+        <v>4889</v>
+      </c>
+      <c r="B992" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C992" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D992" t="s">
+        <v>30</v>
+      </c>
+      <c r="E992" t="s">
+        <v>4890</v>
+      </c>
+      <c r="F992" t="s">
+        <v>33</v>
+      </c>
+      <c r="G992" t="s">
+        <v>483</v>
+      </c>
+      <c r="H992" t="s">
+        <v>4891</v>
+      </c>
+      <c r="I992" t="s">
+        <v>4892</v>
+      </c>
+      <c r="J992" t="s">
+        <v>26</v>
+      </c>
+      <c r="K992" t="s">
+        <v>4893</v>
+      </c>
+      <c r="L992" t="s">
+        <v>30</v>
+      </c>
+      <c r="M992" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N992" t="s">
+        <v>30</v>
+      </c>
+      <c r="O992" t="s">
+        <v>30</v>
+      </c>
+      <c r="P992" t="s">
+        <v>4865</v>
+      </c>
+    </row>
+    <row r="993" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A993" t="s">
+        <v>4894</v>
+      </c>
+      <c r="B993" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C993" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D993" t="s">
+        <v>30</v>
+      </c>
+      <c r="E993" t="s">
+        <v>4895</v>
+      </c>
+      <c r="F993" t="s">
+        <v>48</v>
+      </c>
+      <c r="G993" t="s">
+        <v>4896</v>
+      </c>
+      <c r="H993" t="s">
+        <v>4897</v>
+      </c>
+      <c r="I993" t="s">
+        <v>4898</v>
+      </c>
+      <c r="J993" t="s">
+        <v>26</v>
+      </c>
+      <c r="K993" t="s">
+        <v>4899</v>
+      </c>
+      <c r="L993" t="s">
+        <v>30</v>
+      </c>
+      <c r="M993" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N993" t="s">
+        <v>30</v>
+      </c>
+      <c r="O993" t="s">
+        <v>30</v>
+      </c>
+      <c r="P993" t="s">
+        <v>4900</v>
+      </c>
+    </row>
+    <row r="994" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A994" t="s">
+        <v>4901</v>
+      </c>
+      <c r="B994" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C994" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D994" t="s">
+        <v>30</v>
+      </c>
+      <c r="E994" t="s">
+        <v>4902</v>
+      </c>
+      <c r="F994" t="s">
+        <v>33</v>
+      </c>
+      <c r="G994" t="s">
+        <v>483</v>
+      </c>
+      <c r="H994" t="s">
+        <v>4903</v>
+      </c>
+      <c r="I994" t="s">
+        <v>4904</v>
+      </c>
+      <c r="J994" t="s">
+        <v>26</v>
+      </c>
+      <c r="K994" t="s">
+        <v>4850</v>
+      </c>
+      <c r="L994" t="s">
+        <v>30</v>
+      </c>
+      <c r="M994" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N994" t="s">
+        <v>30</v>
+      </c>
+      <c r="O994" t="s">
+        <v>30</v>
+      </c>
+      <c r="P994" t="s">
+        <v>4851</v>
+      </c>
+    </row>
+    <row r="995" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A995" t="s">
+        <v>4905</v>
+      </c>
+      <c r="B995" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C995" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D995" t="s">
+        <v>30</v>
+      </c>
+      <c r="E995" t="s">
+        <v>4906</v>
+      </c>
+      <c r="F995" t="s">
+        <v>33</v>
+      </c>
+      <c r="G995" t="s">
+        <v>4715</v>
+      </c>
+      <c r="H995" t="s">
+        <v>4907</v>
+      </c>
+      <c r="I995" t="s">
+        <v>4908</v>
+      </c>
+      <c r="J995" t="s">
+        <v>26</v>
+      </c>
+      <c r="K995" t="s">
+        <v>4909</v>
+      </c>
+      <c r="L995" t="s">
+        <v>30</v>
+      </c>
+      <c r="M995" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N995" t="s">
+        <v>30</v>
+      </c>
+      <c r="O995" t="s">
+        <v>30</v>
+      </c>
+      <c r="P995" t="s">
+        <v>4910</v>
+      </c>
+    </row>
+    <row r="996" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A996" t="s">
+        <v>4911</v>
+      </c>
+      <c r="B996" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C996" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D996" t="s">
+        <v>30</v>
+      </c>
+      <c r="E996" t="s">
+        <v>4912</v>
+      </c>
+      <c r="F996" t="s">
+        <v>33</v>
+      </c>
+      <c r="G996" t="s">
+        <v>4913</v>
+      </c>
+      <c r="H996" t="s">
+        <v>4914</v>
+      </c>
+      <c r="I996" t="s">
+        <v>4915</v>
+      </c>
+      <c r="J996" t="s">
+        <v>26</v>
+      </c>
+      <c r="K996" t="s">
+        <v>4916</v>
+      </c>
+      <c r="L996" t="s">
+        <v>30</v>
+      </c>
+      <c r="M996" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N996" t="s">
+        <v>30</v>
+      </c>
+      <c r="O996" t="s">
+        <v>30</v>
+      </c>
+      <c r="P996" t="s">
+        <v>4917</v>
+      </c>
+    </row>
+    <row r="997" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A997" t="s">
+        <v>4918</v>
+      </c>
+      <c r="B997" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C997" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D997" t="s">
+        <v>30</v>
+      </c>
+      <c r="E997" t="s">
+        <v>4919</v>
+      </c>
+      <c r="F997" t="s">
+        <v>33</v>
+      </c>
+      <c r="G997" t="s">
+        <v>4920</v>
+      </c>
+      <c r="H997" t="s">
+        <v>4921</v>
+      </c>
+      <c r="I997" t="s">
+        <v>4922</v>
+      </c>
+      <c r="J997" t="s">
+        <v>26</v>
+      </c>
+      <c r="K997" t="s">
+        <v>4923</v>
+      </c>
+      <c r="L997" t="s">
+        <v>30</v>
+      </c>
+      <c r="M997" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N997" t="s">
+        <v>30</v>
+      </c>
+      <c r="O997" t="s">
+        <v>30</v>
+      </c>
+      <c r="P997" t="s">
+        <v>4924</v>
+      </c>
+    </row>
+    <row r="998" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A998" t="s">
+        <v>4925</v>
+      </c>
+      <c r="B998" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C998" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D998" t="s">
+        <v>30</v>
+      </c>
+      <c r="E998" t="s">
+        <v>4926</v>
+      </c>
+      <c r="F998" t="s">
+        <v>33</v>
+      </c>
+      <c r="G998" t="s">
+        <v>4927</v>
+      </c>
+      <c r="H998" t="s">
+        <v>4928</v>
+      </c>
+      <c r="I998" t="s">
+        <v>4929</v>
+      </c>
+      <c r="J998" t="s">
+        <v>26</v>
+      </c>
+      <c r="K998" t="s">
+        <v>4930</v>
+      </c>
+      <c r="L998" t="s">
+        <v>30</v>
+      </c>
+      <c r="M998" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N998" t="s">
+        <v>30</v>
+      </c>
+      <c r="O998" t="s">
+        <v>30</v>
+      </c>
+      <c r="P998" t="s">
+        <v>4931</v>
+      </c>
+    </row>
+    <row r="999" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A999" t="s">
+        <v>4932</v>
+      </c>
+      <c r="B999" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C999" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D999" t="s">
+        <v>30</v>
+      </c>
+      <c r="E999" t="s">
+        <v>4933</v>
+      </c>
+      <c r="F999" t="s">
+        <v>48</v>
+      </c>
+      <c r="G999" t="s">
+        <v>4934</v>
+      </c>
+      <c r="H999" t="s">
+        <v>4935</v>
+      </c>
+      <c r="I999" t="s">
+        <v>4936</v>
+      </c>
+      <c r="J999" t="s">
+        <v>26</v>
+      </c>
+      <c r="K999" t="s">
+        <v>4937</v>
+      </c>
+      <c r="L999" t="s">
+        <v>30</v>
+      </c>
+      <c r="M999" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N999" t="s">
+        <v>30</v>
+      </c>
+      <c r="O999" t="s">
+        <v>30</v>
+      </c>
+      <c r="P999" t="s">
+        <v>4924</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1000" t="s">
+        <v>4938</v>
+      </c>
+      <c r="B1000" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1000" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D1000" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1000" t="s">
+        <v>4939</v>
+      </c>
+      <c r="F1000" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1000" t="s">
+        <v>4940</v>
+      </c>
+      <c r="H1000" t="s">
+        <v>4941</v>
+      </c>
+      <c r="I1000" t="s">
+        <v>4942</v>
+      </c>
+      <c r="J1000" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1000" t="s">
+        <v>4923</v>
+      </c>
+      <c r="L1000" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1000" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1000" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1000" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1000" t="s">
+        <v>4924</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1001" t="s">
+        <v>4943</v>
+      </c>
+      <c r="B1001" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1001" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D1001" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1001" t="s">
+        <v>4944</v>
+      </c>
+      <c r="F1001" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1001" t="s">
+        <v>4945</v>
+      </c>
+      <c r="H1001" t="s">
+        <v>4946</v>
+      </c>
+      <c r="I1001" t="s">
+        <v>4947</v>
+      </c>
+      <c r="J1001" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1001" t="s">
+        <v>4948</v>
+      </c>
+      <c r="L1001" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1001" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1001" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1001" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1001" t="s">
+        <v>4924</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1002" t="s">
+        <v>4949</v>
+      </c>
+      <c r="B1002" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1002" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D1002" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1002" t="s">
+        <v>4950</v>
+      </c>
+      <c r="F1002" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1002" t="s">
+        <v>4951</v>
+      </c>
+      <c r="H1002" t="s">
+        <v>4952</v>
+      </c>
+      <c r="I1002" t="s">
+        <v>4953</v>
+      </c>
+      <c r="J1002" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1002" t="s">
+        <v>4954</v>
+      </c>
+      <c r="L1002" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1002" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1002" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1002" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1002" t="s">
+        <v>4955</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1003" t="s">
+        <v>4956</v>
+      </c>
+      <c r="B1003" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1003" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D1003" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1003" t="s">
+        <v>4957</v>
+      </c>
+      <c r="F1003" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1003" t="s">
+        <v>4958</v>
+      </c>
+      <c r="H1003" t="s">
+        <v>4959</v>
+      </c>
+      <c r="I1003" t="s">
+        <v>4960</v>
+      </c>
+      <c r="J1003" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1003" t="s">
+        <v>4961</v>
+      </c>
+      <c r="L1003" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1003" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1003" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1003" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1003" t="s">
+        <v>4910</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1004" t="s">
+        <v>4962</v>
+      </c>
+      <c r="B1004" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1004" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D1004" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1004" t="s">
+        <v>4963</v>
+      </c>
+      <c r="F1004" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1004" t="s">
+        <v>4715</v>
+      </c>
+      <c r="H1004" t="s">
+        <v>4964</v>
+      </c>
+      <c r="I1004" t="s">
+        <v>4965</v>
+      </c>
+      <c r="J1004" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1004" t="s">
+        <v>4723</v>
+      </c>
+      <c r="L1004" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1004" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1004" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1004" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1004" t="s">
+        <v>4773</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1005" t="s">
+        <v>4966</v>
+      </c>
+      <c r="B1005" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1005" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D1005" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1005" t="s">
+        <v>4967</v>
+      </c>
+      <c r="F1005" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1005" t="s">
+        <v>4968</v>
+      </c>
+      <c r="H1005" t="s">
+        <v>4969</v>
+      </c>
+      <c r="I1005" t="s">
+        <v>4970</v>
+      </c>
+      <c r="J1005" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1005" t="s">
+        <v>4871</v>
+      </c>
+      <c r="L1005" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1005" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1005" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1005" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1005" t="s">
+        <v>4872</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1006" t="s">
+        <v>4971</v>
+      </c>
+      <c r="B1006" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1006" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D1006" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1006" t="s">
+        <v>4972</v>
+      </c>
+      <c r="F1006" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1006" t="s">
+        <v>4927</v>
+      </c>
+      <c r="H1006" t="s">
+        <v>4973</v>
+      </c>
+      <c r="I1006" t="s">
+        <v>4974</v>
+      </c>
+      <c r="J1006" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1006" t="s">
+        <v>4923</v>
+      </c>
+      <c r="L1006" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1006" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1006" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1006" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1006" t="s">
+        <v>4931</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1007" t="s">
+        <v>4975</v>
+      </c>
+      <c r="B1007" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1007" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D1007" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1007" t="s">
+        <v>4976</v>
+      </c>
+      <c r="F1007" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1007" t="s">
+        <v>4977</v>
+      </c>
+      <c r="H1007" t="s">
+        <v>4978</v>
+      </c>
+      <c r="I1007" t="s">
+        <v>4979</v>
+      </c>
+      <c r="J1007" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1007" t="s">
+        <v>4980</v>
+      </c>
+      <c r="L1007" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1007" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1007" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1007" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1007" t="s">
+        <v>4981</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1008" t="s">
+        <v>4982</v>
+      </c>
+      <c r="B1008" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1008" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D1008" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1008" t="s">
+        <v>4983</v>
+      </c>
+      <c r="F1008" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1008" t="s">
+        <v>4128</v>
+      </c>
+      <c r="H1008" t="s">
+        <v>4984</v>
+      </c>
+      <c r="I1008" t="s">
+        <v>4985</v>
+      </c>
+      <c r="J1008" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1008" t="s">
+        <v>4850</v>
+      </c>
+      <c r="L1008" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1008" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1008" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1008" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1008" t="s">
+        <v>4851</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1009" t="s">
+        <v>4986</v>
+      </c>
+      <c r="B1009" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1009" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D1009" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1009" t="s">
+        <v>4987</v>
+      </c>
+      <c r="F1009" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1009" t="s">
+        <v>4988</v>
+      </c>
+      <c r="H1009" t="s">
+        <v>4989</v>
+      </c>
+      <c r="I1009" t="s">
+        <v>4990</v>
+      </c>
+      <c r="J1009" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1009" t="s">
+        <v>4730</v>
+      </c>
+      <c r="L1009" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1009" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1009" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1009" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1009" t="s">
+        <v>4748</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1010" t="s">
+        <v>4991</v>
+      </c>
+      <c r="B1010" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1010" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D1010" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1010" t="s">
+        <v>4992</v>
+      </c>
+      <c r="F1010" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1010" t="s">
+        <v>4715</v>
+      </c>
+      <c r="H1010" t="s">
+        <v>4993</v>
+      </c>
+      <c r="I1010" t="s">
+        <v>4994</v>
+      </c>
+      <c r="J1010" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1010" t="s">
+        <v>4723</v>
+      </c>
+      <c r="L1010" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1010" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1010" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1010" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1010" t="s">
+        <v>4701</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1011" t="s">
+        <v>4995</v>
+      </c>
+      <c r="B1011" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1011" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D1011" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1011" t="s">
+        <v>4996</v>
+      </c>
+      <c r="F1011" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1011" t="s">
+        <v>4997</v>
+      </c>
+      <c r="H1011" t="s">
+        <v>4998</v>
+      </c>
+      <c r="I1011" t="s">
+        <v>4999</v>
+      </c>
+      <c r="J1011" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1011" t="s">
+        <v>4723</v>
+      </c>
+      <c r="L1011" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1011" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1011" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1011" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1011" t="s">
+        <v>4701</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1012" t="s">
+        <v>5000</v>
+      </c>
+      <c r="B1012" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1012" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D1012" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1012" t="s">
+        <v>5001</v>
+      </c>
+      <c r="F1012" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1012" t="s">
+        <v>5002</v>
+      </c>
+      <c r="H1012" t="s">
+        <v>5003</v>
+      </c>
+      <c r="I1012" t="s">
+        <v>5004</v>
+      </c>
+      <c r="J1012" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1012" t="s">
+        <v>5005</v>
+      </c>
+      <c r="L1012" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1012" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1012" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1012" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1012" t="s">
+        <v>5006</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1013" t="s">
+        <v>5007</v>
+      </c>
+      <c r="B1013" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1013" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D1013" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1013" t="s">
+        <v>5008</v>
+      </c>
+      <c r="F1013" t="s">
+        <v>172</v>
+      </c>
+      <c r="G1013" t="s">
+        <v>5009</v>
+      </c>
+      <c r="H1013" t="s">
+        <v>5010</v>
+      </c>
+      <c r="I1013" t="s">
+        <v>5011</v>
+      </c>
+      <c r="J1013" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1013" t="s">
+        <v>5012</v>
+      </c>
+      <c r="L1013" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1013" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1013" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1013" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1013" t="s">
+        <v>4865</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1014" t="s">
+        <v>5013</v>
+      </c>
+      <c r="B1014" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1014" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1014" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1014" t="s">
+        <v>5014</v>
+      </c>
+      <c r="F1014" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1014" t="s">
+        <v>5015</v>
+      </c>
+      <c r="H1014" t="s">
+        <v>5016</v>
+      </c>
+      <c r="I1014" t="s">
+        <v>5017</v>
+      </c>
+      <c r="J1014" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1014" t="s">
+        <v>5018</v>
+      </c>
+      <c r="L1014" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1014" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1014" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1014" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1014" t="s">
+        <v>5019</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1015" t="s">
+        <v>5020</v>
+      </c>
+      <c r="B1015" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1015" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1015" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1015" t="s">
+        <v>5021</v>
+      </c>
+      <c r="F1015" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1015" t="s">
+        <v>5022</v>
+      </c>
+      <c r="H1015" t="s">
+        <v>5023</v>
+      </c>
+      <c r="I1015" t="s">
+        <v>5024</v>
+      </c>
+      <c r="J1015" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1015" t="s">
+        <v>5025</v>
+      </c>
+      <c r="L1015" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1015" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1015" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1015" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1015" t="s">
+        <v>5026</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1016" t="s">
+        <v>5027</v>
+      </c>
+      <c r="B1016" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1016" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1016" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1016" t="s">
+        <v>5028</v>
+      </c>
+      <c r="F1016" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1016" t="s">
+        <v>5029</v>
+      </c>
+      <c r="H1016" t="s">
+        <v>5030</v>
+      </c>
+      <c r="I1016" t="s">
+        <v>5031</v>
+      </c>
+      <c r="J1016" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1016" t="s">
+        <v>5032</v>
+      </c>
+      <c r="L1016" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1016" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1016" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1016" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1016" t="s">
+        <v>4217</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1017" t="s">
+        <v>5033</v>
+      </c>
+      <c r="B1017" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1017" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1017" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1017" t="s">
+        <v>5034</v>
+      </c>
+      <c r="F1017" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1017" t="s">
+        <v>5035</v>
+      </c>
+      <c r="H1017" t="s">
+        <v>5036</v>
+      </c>
+      <c r="I1017" t="s">
+        <v>5037</v>
+      </c>
+      <c r="J1017" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1017" t="s">
+        <v>5038</v>
+      </c>
+      <c r="L1017" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1017" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1017" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1017" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1017" t="s">
+        <v>5039</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1018" t="s">
+        <v>5040</v>
+      </c>
+      <c r="B1018" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1018" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1018" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1018" t="s">
+        <v>5041</v>
+      </c>
+      <c r="F1018" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1018" t="s">
+        <v>5042</v>
+      </c>
+      <c r="H1018" t="s">
+        <v>5043</v>
+      </c>
+      <c r="I1018" t="s">
+        <v>5044</v>
+      </c>
+      <c r="J1018" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1018" t="s">
+        <v>5045</v>
+      </c>
+      <c r="L1018" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1018" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1018" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1018" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1018" t="s">
+        <v>5039</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1019" t="s">
+        <v>5046</v>
+      </c>
+      <c r="B1019" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1019" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1019" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1019" t="s">
+        <v>5047</v>
+      </c>
+      <c r="F1019" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1019" t="s">
+        <v>5035</v>
+      </c>
+      <c r="H1019" t="s">
+        <v>5048</v>
+      </c>
+      <c r="I1019" t="s">
+        <v>5049</v>
+      </c>
+      <c r="J1019" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1019" t="s">
+        <v>5050</v>
+      </c>
+      <c r="L1019" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1019" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1019" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1019" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1019" t="s">
+        <v>5051</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1020" t="s">
+        <v>5052</v>
+      </c>
+      <c r="B1020" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1020" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1020" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1020" t="s">
+        <v>5053</v>
+      </c>
+      <c r="F1020" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1020" t="s">
+        <v>5054</v>
+      </c>
+      <c r="H1020" t="s">
+        <v>5055</v>
+      </c>
+      <c r="I1020" t="s">
+        <v>5056</v>
+      </c>
+      <c r="J1020" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1020" t="s">
+        <v>5057</v>
+      </c>
+      <c r="L1020" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1020" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1020" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1020" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1020" t="s">
+        <v>5051</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1021" t="s">
+        <v>5058</v>
+      </c>
+      <c r="B1021" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1021" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1021" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1021" t="s">
+        <v>5059</v>
+      </c>
+      <c r="F1021" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1021" t="s">
+        <v>5060</v>
+      </c>
+      <c r="H1021" t="s">
+        <v>5061</v>
+      </c>
+      <c r="I1021" t="s">
+        <v>5062</v>
+      </c>
+      <c r="J1021" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1021" t="s">
+        <v>5063</v>
+      </c>
+      <c r="L1021" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1021" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1021" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1021" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1021" t="s">
+        <v>5051</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1022" t="s">
+        <v>5064</v>
+      </c>
+      <c r="B1022" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1022" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1022" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1022" t="s">
+        <v>5065</v>
+      </c>
+      <c r="F1022" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1022" t="s">
+        <v>5035</v>
+      </c>
+      <c r="H1022" t="s">
+        <v>5066</v>
+      </c>
+      <c r="I1022" t="s">
+        <v>5067</v>
+      </c>
+      <c r="J1022" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1022" t="s">
+        <v>5068</v>
+      </c>
+      <c r="L1022" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1022" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1022" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1022" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1022" t="s">
+        <v>5069</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1023" t="s">
+        <v>5070</v>
+      </c>
+      <c r="B1023" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1023" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1023" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1023" t="s">
+        <v>5071</v>
+      </c>
+      <c r="F1023" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1023" t="s">
+        <v>5072</v>
+      </c>
+      <c r="H1023" t="s">
+        <v>5073</v>
+      </c>
+      <c r="I1023" t="s">
+        <v>5074</v>
+      </c>
+      <c r="J1023" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1023" t="s">
+        <v>5075</v>
+      </c>
+      <c r="L1023" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1023" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1023" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1023" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1023" t="s">
+        <v>5076</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1024" t="s">
+        <v>5077</v>
+      </c>
+      <c r="B1024" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1024" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1024" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1024" t="s">
+        <v>5078</v>
+      </c>
+      <c r="F1024" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1024" t="s">
+        <v>5035</v>
+      </c>
+      <c r="H1024" t="s">
+        <v>5079</v>
+      </c>
+      <c r="I1024" t="s">
+        <v>5080</v>
+      </c>
+      <c r="J1024" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1024" t="s">
+        <v>5038</v>
+      </c>
+      <c r="L1024" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1024" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1024" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1024" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1024" t="s">
+        <v>5039</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1025" t="s">
+        <v>5081</v>
+      </c>
+      <c r="B1025" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1025" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1025" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1025" t="s">
+        <v>5082</v>
+      </c>
+      <c r="F1025" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1025" t="s">
+        <v>5083</v>
+      </c>
+      <c r="H1025" t="s">
+        <v>5084</v>
+      </c>
+      <c r="I1025" t="s">
+        <v>5085</v>
+      </c>
+      <c r="J1025" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1025" t="s">
+        <v>5086</v>
+      </c>
+      <c r="L1025" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1025" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1025" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1025" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1025" t="s">
+        <v>5051</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1026" t="s">
+        <v>5087</v>
+      </c>
+      <c r="B1026" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1026" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1026" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1026" t="s">
+        <v>5088</v>
+      </c>
+      <c r="F1026" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1026" t="s">
+        <v>5089</v>
+      </c>
+      <c r="H1026" t="s">
+        <v>5090</v>
+      </c>
+      <c r="I1026" t="s">
+        <v>5091</v>
+      </c>
+      <c r="J1026" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1026" t="s">
+        <v>5092</v>
+      </c>
+      <c r="L1026" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1026" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1026" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1026" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1026" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1027" t="s">
+        <v>5093</v>
+      </c>
+      <c r="B1027" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1027" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1027" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1027" t="s">
+        <v>5094</v>
+      </c>
+      <c r="F1027" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1027" t="s">
+        <v>5095</v>
+      </c>
+      <c r="H1027" t="s">
+        <v>5096</v>
+      </c>
+      <c r="I1027" t="s">
+        <v>5097</v>
+      </c>
+      <c r="J1027" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1027" t="s">
+        <v>5098</v>
+      </c>
+      <c r="L1027" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1027" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1027" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1027" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1027" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1028" t="s">
+        <v>5099</v>
+      </c>
+      <c r="B1028" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1028" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1028" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1028" t="s">
+        <v>5100</v>
+      </c>
+      <c r="F1028" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1028" t="s">
+        <v>5101</v>
+      </c>
+      <c r="H1028" t="s">
+        <v>5102</v>
+      </c>
+      <c r="I1028" t="s">
+        <v>5103</v>
+      </c>
+      <c r="J1028" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1028" t="s">
+        <v>5104</v>
+      </c>
+      <c r="L1028" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1028" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1028" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1028" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1028" t="s">
+        <v>5105</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1029" t="s">
+        <v>5106</v>
+      </c>
+      <c r="B1029" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1029" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1029" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1029" t="s">
+        <v>5107</v>
+      </c>
+      <c r="F1029" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1029" t="s">
+        <v>5108</v>
+      </c>
+      <c r="H1029" t="s">
+        <v>5109</v>
+      </c>
+      <c r="I1029" t="s">
+        <v>5110</v>
+      </c>
+      <c r="J1029" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1029" t="s">
+        <v>5111</v>
+      </c>
+      <c r="L1029" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1029" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1029" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1029" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1029" t="s">
+        <v>5112</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1030" t="s">
+        <v>5113</v>
+      </c>
+      <c r="B1030" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1030" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1030" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1030" t="s">
+        <v>5114</v>
+      </c>
+      <c r="F1030" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1030" t="s">
+        <v>5115</v>
+      </c>
+      <c r="H1030" t="s">
+        <v>5116</v>
+      </c>
+      <c r="I1030" t="s">
+        <v>5117</v>
+      </c>
+      <c r="J1030" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1030" t="s">
+        <v>5118</v>
+      </c>
+      <c r="L1030" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1030" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1030" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1030" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1030" t="s">
+        <v>5119</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1031" t="s">
+        <v>5120</v>
+      </c>
+      <c r="B1031" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1031" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1031" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1031" t="s">
+        <v>5121</v>
+      </c>
+      <c r="F1031" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1031" t="s">
+        <v>5122</v>
+      </c>
+      <c r="H1031" t="s">
+        <v>5123</v>
+      </c>
+      <c r="I1031" t="s">
+        <v>5124</v>
+      </c>
+      <c r="J1031" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1031" t="s">
+        <v>5125</v>
+      </c>
+      <c r="L1031" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1031" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1031" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1031" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1031" t="s">
+        <v>5126</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1032" t="s">
+        <v>5127</v>
+      </c>
+      <c r="B1032" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1032" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1032" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1032" t="s">
+        <v>5128</v>
+      </c>
+      <c r="F1032" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1032" t="s">
+        <v>5129</v>
+      </c>
+      <c r="H1032" t="s">
+        <v>5130</v>
+      </c>
+      <c r="I1032" t="s">
+        <v>5131</v>
+      </c>
+      <c r="J1032" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1032" t="s">
+        <v>5132</v>
+      </c>
+      <c r="L1032" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1032" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1032" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1032" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1032" t="s">
+        <v>5133</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1033" t="s">
+        <v>5134</v>
+      </c>
+      <c r="B1033" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1033" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1033" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1033" t="s">
+        <v>5135</v>
+      </c>
+      <c r="F1033" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1033" t="s">
+        <v>5129</v>
+      </c>
+      <c r="H1033" t="s">
+        <v>5136</v>
+      </c>
+      <c r="I1033" t="s">
+        <v>5137</v>
+      </c>
+      <c r="J1033" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1033" t="s">
+        <v>5138</v>
+      </c>
+      <c r="L1033" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1033" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1033" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1033" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1033" t="s">
+        <v>5139</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1034" t="s">
+        <v>5140</v>
+      </c>
+      <c r="B1034" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1034" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1034" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1034" t="s">
+        <v>5141</v>
+      </c>
+      <c r="F1034" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1034" t="s">
+        <v>5142</v>
+      </c>
+      <c r="H1034" t="s">
+        <v>5143</v>
+      </c>
+      <c r="I1034" t="s">
+        <v>5144</v>
+      </c>
+      <c r="J1034" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1034" t="s">
+        <v>5145</v>
+      </c>
+      <c r="L1034" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1034" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1034" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1034" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1034" t="s">
+        <v>5146</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1035" t="s">
+        <v>5147</v>
+      </c>
+      <c r="B1035" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1035" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1035" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1035" t="s">
+        <v>5148</v>
+      </c>
+      <c r="F1035" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1035" t="s">
+        <v>5149</v>
+      </c>
+      <c r="H1035" t="s">
+        <v>5150</v>
+      </c>
+      <c r="I1035" t="s">
+        <v>5151</v>
+      </c>
+      <c r="J1035" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1035" t="s">
+        <v>5152</v>
+      </c>
+      <c r="L1035" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1035" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1035" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1035" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1035" t="s">
+        <v>5153</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1036" t="s">
+        <v>5154</v>
+      </c>
+      <c r="B1036" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1036" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1036" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1036" t="s">
+        <v>5155</v>
+      </c>
+      <c r="F1036" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1036" t="s">
+        <v>5156</v>
+      </c>
+      <c r="H1036" t="s">
+        <v>5157</v>
+      </c>
+      <c r="I1036" t="s">
+        <v>5158</v>
+      </c>
+      <c r="J1036" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1036" t="s">
+        <v>5159</v>
+      </c>
+      <c r="L1036" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1036" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1036" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1036" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1036" t="s">
+        <v>5160</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1037" t="s">
+        <v>5161</v>
+      </c>
+      <c r="B1037" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1037" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1037" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1037" t="s">
+        <v>5162</v>
+      </c>
+      <c r="F1037" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1037" t="s">
+        <v>5163</v>
+      </c>
+      <c r="H1037" t="s">
+        <v>5164</v>
+      </c>
+      <c r="I1037" t="s">
+        <v>5165</v>
+      </c>
+      <c r="J1037" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1037" t="s">
+        <v>5166</v>
+      </c>
+      <c r="L1037" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1037" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1037" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1037" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1037" t="s">
+        <v>5160</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1038" t="s">
+        <v>5167</v>
+      </c>
+      <c r="B1038" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1038" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1038" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1038" t="s">
+        <v>5168</v>
+      </c>
+      <c r="F1038" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1038" t="s">
+        <v>5169</v>
+      </c>
+      <c r="H1038" t="s">
+        <v>5170</v>
+      </c>
+      <c r="I1038" t="s">
+        <v>5171</v>
+      </c>
+      <c r="J1038" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1038" t="s">
+        <v>5172</v>
+      </c>
+      <c r="L1038" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1038" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1038" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1038" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1038" t="s">
+        <v>5173</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1039" t="s">
+        <v>5174</v>
+      </c>
+      <c r="B1039" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1039" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1039" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1039" t="s">
+        <v>5175</v>
+      </c>
+      <c r="F1039" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1039" t="s">
+        <v>5176</v>
+      </c>
+      <c r="H1039" t="s">
+        <v>5177</v>
+      </c>
+      <c r="I1039" t="s">
+        <v>5178</v>
+      </c>
+      <c r="J1039" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1039" t="s">
+        <v>5179</v>
+      </c>
+      <c r="L1039" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1039" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1039" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1039" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1039" t="s">
+        <v>5180</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1040" t="s">
+        <v>5181</v>
+      </c>
+      <c r="B1040" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1040" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1040" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1040" t="s">
+        <v>5182</v>
+      </c>
+      <c r="F1040" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1040" t="s">
+        <v>5183</v>
+      </c>
+      <c r="H1040" t="s">
+        <v>5184</v>
+      </c>
+      <c r="I1040" t="s">
+        <v>5185</v>
+      </c>
+      <c r="J1040" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1040" t="s">
+        <v>5186</v>
+      </c>
+      <c r="L1040" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1040" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1040" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1040" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1040" t="s">
+        <v>5187</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1041" t="s">
+        <v>5188</v>
+      </c>
+      <c r="B1041" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1041" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1041" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1041" t="s">
+        <v>5189</v>
+      </c>
+      <c r="F1041" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1041" t="s">
+        <v>5190</v>
+      </c>
+      <c r="H1041" t="s">
+        <v>5191</v>
+      </c>
+      <c r="I1041" t="s">
+        <v>5192</v>
+      </c>
+      <c r="J1041" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1041" t="s">
+        <v>5193</v>
+      </c>
+      <c r="L1041" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1041" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1041" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1041" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1041" t="s">
+        <v>5194</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1042" t="s">
+        <v>5195</v>
+      </c>
+      <c r="B1042" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1042" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1042" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1042" t="s">
+        <v>5196</v>
+      </c>
+      <c r="F1042" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1042" t="s">
+        <v>5197</v>
+      </c>
+      <c r="H1042" t="s">
+        <v>5198</v>
+      </c>
+      <c r="I1042" t="s">
+        <v>5199</v>
+      </c>
+      <c r="J1042" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1042" t="s">
+        <v>5200</v>
+      </c>
+      <c r="L1042" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1042" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1042" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1042" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1042" t="s">
+        <v>5201</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1043" t="s">
+        <v>5202</v>
+      </c>
+      <c r="B1043" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1043" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1043" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1043" t="s">
+        <v>5203</v>
+      </c>
+      <c r="F1043" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1043" t="s">
+        <v>5204</v>
+      </c>
+      <c r="H1043" t="s">
+        <v>5205</v>
+      </c>
+      <c r="I1043" t="s">
+        <v>5206</v>
+      </c>
+      <c r="J1043" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1043" t="s">
+        <v>5207</v>
+      </c>
+      <c r="L1043" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1043" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1043" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1043" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1043" t="s">
+        <v>5208</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1044" t="s">
+        <v>5209</v>
+      </c>
+      <c r="B1044" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1044" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1044" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1044" t="s">
+        <v>5210</v>
+      </c>
+      <c r="F1044" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1044" t="s">
+        <v>5211</v>
+      </c>
+      <c r="H1044" t="s">
+        <v>5212</v>
+      </c>
+      <c r="I1044" t="s">
+        <v>5213</v>
+      </c>
+      <c r="J1044" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1044" t="s">
+        <v>5214</v>
+      </c>
+      <c r="L1044" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1044" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1044" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1044" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1044" t="s">
+        <v>5215</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1045" t="s">
+        <v>5216</v>
+      </c>
+      <c r="B1045" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1045" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1045" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1045" t="s">
+        <v>5217</v>
+      </c>
+      <c r="F1045" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1045" t="s">
+        <v>5218</v>
+      </c>
+      <c r="H1045" t="s">
+        <v>5219</v>
+      </c>
+      <c r="I1045" t="s">
+        <v>5220</v>
+      </c>
+      <c r="J1045" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1045" t="s">
+        <v>5221</v>
+      </c>
+      <c r="L1045" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1045" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1045" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1045" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1045" t="s">
+        <v>5222</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1046" t="s">
+        <v>5223</v>
+      </c>
+      <c r="B1046" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1046" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1046" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1046" t="s">
+        <v>5224</v>
+      </c>
+      <c r="F1046" t="s">
+        <v>172</v>
+      </c>
+      <c r="G1046" t="s">
+        <v>4220</v>
+      </c>
+      <c r="H1046" t="s">
+        <v>5225</v>
+      </c>
+      <c r="I1046" t="s">
+        <v>5226</v>
+      </c>
+      <c r="J1046" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1046" t="s">
+        <v>5227</v>
+      </c>
+      <c r="L1046" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1046" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1046" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1046" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1046" t="s">
+        <v>5019</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1047" t="s">
+        <v>5228</v>
+      </c>
+      <c r="B1047" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1047" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1047" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1047" t="s">
+        <v>5229</v>
+      </c>
+      <c r="F1047" t="s">
+        <v>172</v>
+      </c>
+      <c r="G1047" t="s">
+        <v>5230</v>
+      </c>
+      <c r="H1047" t="s">
+        <v>5231</v>
+      </c>
+      <c r="I1047" t="s">
+        <v>5232</v>
+      </c>
+      <c r="J1047" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1047" t="s">
+        <v>5233</v>
+      </c>
+      <c r="L1047" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1047" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1047" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1047" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1047" t="s">
+        <v>5234</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1048" t="s">
+        <v>5235</v>
+      </c>
+      <c r="B1048" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1048" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1048" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1048" t="s">
+        <v>5236</v>
+      </c>
+      <c r="F1048" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1048" t="s">
+        <v>5035</v>
+      </c>
+      <c r="H1048" t="s">
+        <v>5237</v>
+      </c>
+      <c r="I1048" t="s">
+        <v>5238</v>
+      </c>
+      <c r="J1048" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1048" t="s">
+        <v>5239</v>
+      </c>
+      <c r="L1048" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1048" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1048" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1048" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1048" t="s">
+        <v>5039</v>
       </c>
     </row>
   </sheetData>
@@ -63060,7 +69195,7 @@
         <v>2</v>
       </c>
       <c r="C1" s="32" t="s">
-        <v>4695</v>
+        <v>5240</v>
       </c>
       <c r="D1" s="32" t="s">
         <v>53</v>
@@ -63093,7 +69228,7 @@
         <v>9</v>
       </c>
       <c r="N1" s="32" t="s">
-        <v>4696</v>
+        <v>5241</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -63137,7 +69272,7 @@
         <v>39</v>
       </c>
       <c r="N2" s="34" t="s">
-        <v>4697</v>
+        <v>5242</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -63181,7 +69316,7 @@
         <v>36</v>
       </c>
       <c r="N3" s="36" t="s">
-        <v>4697</v>
+        <v>5242</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -63225,7 +69360,7 @@
         <v>35</v>
       </c>
       <c r="N4" s="34" t="s">
-        <v>4697</v>
+        <v>5242</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -63269,7 +69404,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="36" t="s">
-        <v>4698</v>
+        <v>5243</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -63313,7 +69448,7 @@
         <v>33</v>
       </c>
       <c r="N6" s="34" t="s">
-        <v>4697</v>
+        <v>5242</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -63357,7 +69492,7 @@
         <v>22</v>
       </c>
       <c r="N7" s="36" t="s">
-        <v>4697</v>
+        <v>5242</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -63401,7 +69536,7 @@
         <v>36</v>
       </c>
       <c r="N8" s="34" t="s">
-        <v>4697</v>
+        <v>5242</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -63445,7 +69580,7 @@
         <v>34</v>
       </c>
       <c r="N9" s="36" t="s">
-        <v>4697</v>
+        <v>5242</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -63489,7 +69624,7 @@
         <v>36</v>
       </c>
       <c r="N10" s="34" t="s">
-        <v>4697</v>
+        <v>5242</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -63533,12 +69668,12 @@
         <v>29</v>
       </c>
       <c r="N11" s="36" t="s">
-        <v>4697</v>
+        <v>5242</v>
       </c>
     </row>
     <row r="13" spans="1:14" s="37" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="37" t="s">
-        <v>4699</v>
+        <v>5244</v>
       </c>
       <c r="B13" s="37" t="s">
         <v>30</v>
@@ -63550,7 +69685,7 @@
         <v>300</v>
       </c>
       <c r="N13" s="37" t="s">
-        <v>4700</v>
+        <v>5245</v>
       </c>
     </row>
   </sheetData>
@@ -63574,7 +69709,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="32" t="s">
-        <v>4701</v>
+        <v>5246</v>
       </c>
       <c r="C1" s="32" t="s">
         <v>9</v>
@@ -63681,7 +69816,7 @@
     </row>
     <row r="12" spans="1:3" s="37" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="37" t="s">
-        <v>4702</v>
+        <v>5247</v>
       </c>
       <c r="B12" s="37">
         <v>332</v>

--- a/manual-qa-repository/07-execution/TestCases-Consolidated.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-Consolidated.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16678" uniqueCount="5248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17382" uniqueCount="5292">
   <si>
     <t>TC ID</t>
   </si>
@@ -16413,6 +16413,138 @@
   </si>
   <si>
     <t>SM-FS §1.6, INDEX.md "Debounce"</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_FUNC_002</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_NEG_003</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_NEG_009</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_VAL_010</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_UI_013</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_UI_014</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_NEG_016</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_UI_017</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_FUNC_018</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_UI_019</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_UI_020</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_UI_021</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_UI_022</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_UI_023</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_UI_024</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_UI_025</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_UI_026</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_FUNC_028</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_UI_029</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_FUNC_030</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_FUNC_031</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_FUNC_032</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_VAL_034</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_VAL_035</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_FUNC_036</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_FUNC_037</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_FUNC_038</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_FUNC_039</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_FUNC_040</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_UI_041</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_FUNC_042</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_UI_043</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_NEG_044</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_FUNC_045</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_FUNC_046</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_E2E_047</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_VAL_048</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_VAL_049</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_E2E_050</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_E2E_051</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_BIZ_052</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_BIZ_053</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_NEG_054</t>
+  </si>
+  <si>
+    <t>TC_PHYSALLOC_UI_055</t>
   </si>
   <si>
     <t>Total TCs</t>
@@ -17035,7 +17167,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P1048"/>
+  <dimension ref="A1:P1092"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -69153,6 +69285,2206 @@
       </c>
       <c r="P1048" t="s">
         <v>5039</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1049" t="s">
+        <v>5240</v>
+      </c>
+      <c r="B1049" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1049" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1049" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1049" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1049" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1049" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1049" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1049" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1049" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1049" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1049" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1049" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1049" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1049" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1049" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1050" t="s">
+        <v>5241</v>
+      </c>
+      <c r="B1050" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1050" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1050" t="s">
+        <v>148</v>
+      </c>
+      <c r="E1050" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1050" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1050" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1050" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1050" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1050" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1050" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1050" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1050" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1050" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1050" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1050" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1051" t="s">
+        <v>5242</v>
+      </c>
+      <c r="B1051" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1051" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1051" t="s">
+        <v>148</v>
+      </c>
+      <c r="E1051" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1051" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1051" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1051" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1051" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1051" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1051" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1051" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1051" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1051" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1051" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1051" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1052" t="s">
+        <v>5243</v>
+      </c>
+      <c r="B1052" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1052" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1052" t="s">
+        <v>119</v>
+      </c>
+      <c r="E1052" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1052" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1052" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1052" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1052" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1052" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1052" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1052" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1052" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1052" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1052" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1052" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1053" t="s">
+        <v>5244</v>
+      </c>
+      <c r="B1053" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1053" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1053" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1053" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1053" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1053" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1053" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1053" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1053" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1053" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1053" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1053" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1053" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1053" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1053" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1054" t="s">
+        <v>5245</v>
+      </c>
+      <c r="B1054" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1054" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1054" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1054" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1054" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1054" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1054" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1054" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1054" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1054" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1054" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1054" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1054" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1054" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1054" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1055" t="s">
+        <v>5246</v>
+      </c>
+      <c r="B1055" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1055" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1055" t="s">
+        <v>148</v>
+      </c>
+      <c r="E1055" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1055" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1055" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1055" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1055" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1055" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1055" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1055" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1055" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1055" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1055" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1055" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1056" t="s">
+        <v>5247</v>
+      </c>
+      <c r="B1056" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1056" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1056" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1056" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1056" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1056" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1056" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1056" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1056" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1056" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1056" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1056" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1056" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1056" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1056" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1057" t="s">
+        <v>5248</v>
+      </c>
+      <c r="B1057" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1057" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1057" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1057" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1057" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1057" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1057" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1057" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1057" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1057" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1057" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1057" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1057" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1057" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1057" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1058" t="s">
+        <v>5249</v>
+      </c>
+      <c r="B1058" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1058" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1058" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1058" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1058" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1058" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1058" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1058" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1058" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1058" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1058" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1058" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1058" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1058" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1058" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1059" t="s">
+        <v>5250</v>
+      </c>
+      <c r="B1059" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1059" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1059" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1059" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1059" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1059" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1059" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1059" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1059" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1059" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1059" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1059" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1059" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1059" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1059" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1060" t="s">
+        <v>5251</v>
+      </c>
+      <c r="B1060" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1060" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1060" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1060" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1060" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1060" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1060" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1060" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1060" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1060" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1060" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1060" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1060" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1060" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1060" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1061" t="s">
+        <v>5252</v>
+      </c>
+      <c r="B1061" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1061" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1061" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1061" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1061" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1061" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1061" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1061" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1061" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1061" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1061" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1061" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1061" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1061" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1061" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1062" t="s">
+        <v>5253</v>
+      </c>
+      <c r="B1062" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1062" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1062" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1062" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1062" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1062" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1062" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1062" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1062" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1062" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1062" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1062" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1062" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1062" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1062" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1063" t="s">
+        <v>5254</v>
+      </c>
+      <c r="B1063" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1063" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1063" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1063" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1063" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1063" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1063" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1063" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1063" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1063" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1063" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1063" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1063" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1063" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1063" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1064" t="s">
+        <v>5255</v>
+      </c>
+      <c r="B1064" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1064" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1064" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1064" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1064" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1064" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1064" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1064" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1064" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1064" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1064" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1064" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1064" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1064" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1064" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1065" t="s">
+        <v>5256</v>
+      </c>
+      <c r="B1065" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1065" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1065" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1065" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1065" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1065" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1065" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1065" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1065" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1065" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1065" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1065" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1065" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1065" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1065" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1066" t="s">
+        <v>5257</v>
+      </c>
+      <c r="B1066" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1066" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1066" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1066" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1066" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1066" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1066" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1066" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1066" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1066" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1066" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1066" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1066" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1066" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1066" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1067" t="s">
+        <v>5258</v>
+      </c>
+      <c r="B1067" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1067" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1067" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1067" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1067" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1067" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1067" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1067" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1067" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1067" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1067" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1067" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1067" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1067" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1067" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1068" t="s">
+        <v>5259</v>
+      </c>
+      <c r="B1068" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1068" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1068" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1068" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1068" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1068" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1068" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1068" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1068" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1068" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1068" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1068" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1068" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1068" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1068" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1069" t="s">
+        <v>5260</v>
+      </c>
+      <c r="B1069" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1069" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1069" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1069" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1069" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1069" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1069" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1069" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1069" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1069" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1069" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1069" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1069" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1069" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1069" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1070" t="s">
+        <v>5261</v>
+      </c>
+      <c r="B1070" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1070" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1070" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1070" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1070" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1070" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1070" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1070" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1070" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1070" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1070" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1070" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1070" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1070" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1070" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1071" t="s">
+        <v>5262</v>
+      </c>
+      <c r="B1071" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1071" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1071" t="s">
+        <v>119</v>
+      </c>
+      <c r="E1071" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1071" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1071" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1071" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1071" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1071" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1071" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1071" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1071" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1071" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1071" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1071" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1072" t="s">
+        <v>5263</v>
+      </c>
+      <c r="B1072" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1072" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1072" t="s">
+        <v>119</v>
+      </c>
+      <c r="E1072" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1072" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1072" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1072" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1072" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1072" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1072" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1072" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1072" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1072" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1072" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1072" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1073" t="s">
+        <v>5264</v>
+      </c>
+      <c r="B1073" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1073" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1073" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1073" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1073" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1073" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1073" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1073" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1073" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1073" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1073" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1073" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1073" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1073" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1073" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1074" t="s">
+        <v>5265</v>
+      </c>
+      <c r="B1074" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1074" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1074" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1074" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1074" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1074" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1074" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1074" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1074" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1074" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1074" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1074" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1074" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1074" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1074" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1075" t="s">
+        <v>5266</v>
+      </c>
+      <c r="B1075" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1075" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1075" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1075" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1075" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1075" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1075" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1075" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1075" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1075" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1075" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1075" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1075" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1075" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1075" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1076" t="s">
+        <v>5267</v>
+      </c>
+      <c r="B1076" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1076" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1076" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1076" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1076" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1076" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1076" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1076" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1076" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1076" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1076" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1076" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1076" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1076" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1076" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1077" t="s">
+        <v>5268</v>
+      </c>
+      <c r="B1077" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1077" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1077" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1077" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1077" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1077" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1077" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1077" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1077" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1077" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1077" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1077" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1077" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1077" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1077" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1078" t="s">
+        <v>5269</v>
+      </c>
+      <c r="B1078" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1078" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1078" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1078" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1078" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1078" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1078" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1078" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1078" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1078" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1078" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1078" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1078" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1078" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1078" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1079" t="s">
+        <v>5270</v>
+      </c>
+      <c r="B1079" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1079" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1079" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1079" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1079" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1079" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1079" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1079" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1079" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1079" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1079" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1079" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1079" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1079" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1079" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1080" t="s">
+        <v>5271</v>
+      </c>
+      <c r="B1080" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1080" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1080" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1080" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1080" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1080" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1080" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1080" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1080" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1080" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1080" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1080" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1080" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1080" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1080" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1081" t="s">
+        <v>5272</v>
+      </c>
+      <c r="B1081" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1081" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1081" t="s">
+        <v>148</v>
+      </c>
+      <c r="E1081" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1081" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1081" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1081" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1081" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1081" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1081" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1081" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1081" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1081" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1081" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1081" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1082" t="s">
+        <v>5273</v>
+      </c>
+      <c r="B1082" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1082" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1082" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1082" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1082" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1082" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1082" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1082" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1082" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1082" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1082" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1082" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1082" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1082" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1082" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1083" t="s">
+        <v>5274</v>
+      </c>
+      <c r="B1083" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1083" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1083" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1083" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1083" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1083" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1083" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1083" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1083" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1083" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1083" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1083" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1083" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1083" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1083" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1084" t="s">
+        <v>5275</v>
+      </c>
+      <c r="B1084" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1084" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1084" t="s">
+        <v>1707</v>
+      </c>
+      <c r="E1084" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1084" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1084" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1084" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1084" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1084" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1084" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1084" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1084" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1084" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1084" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1084" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1085" t="s">
+        <v>5276</v>
+      </c>
+      <c r="B1085" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1085" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1085" t="s">
+        <v>119</v>
+      </c>
+      <c r="E1085" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1085" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1085" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1085" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1085" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1085" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1085" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1085" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1085" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1085" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1085" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1085" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1086" t="s">
+        <v>5277</v>
+      </c>
+      <c r="B1086" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1086" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1086" t="s">
+        <v>119</v>
+      </c>
+      <c r="E1086" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1086" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1086" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1086" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1086" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1086" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1086" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1086" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1086" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1086" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1086" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1086" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1087" t="s">
+        <v>5278</v>
+      </c>
+      <c r="B1087" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1087" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1087" t="s">
+        <v>1707</v>
+      </c>
+      <c r="E1087" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1087" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1087" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1087" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1087" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1087" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1087" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1087" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1087" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1087" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1087" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1087" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1088" t="s">
+        <v>5279</v>
+      </c>
+      <c r="B1088" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1088" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1088" t="s">
+        <v>1707</v>
+      </c>
+      <c r="E1088" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1088" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1088" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1088" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1088" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1088" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1088" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1088" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1088" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1088" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1088" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1088" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1089" t="s">
+        <v>5280</v>
+      </c>
+      <c r="B1089" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1089" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1089" t="s">
+        <v>186</v>
+      </c>
+      <c r="E1089" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1089" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1089" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1089" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1089" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1089" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1089" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1089" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1089" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1089" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1089" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1089" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1090" t="s">
+        <v>5281</v>
+      </c>
+      <c r="B1090" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1090" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1090" t="s">
+        <v>186</v>
+      </c>
+      <c r="E1090" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1090" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1090" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1090" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1090" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1090" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1090" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1090" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1090" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1090" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1090" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1090" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1091" t="s">
+        <v>5282</v>
+      </c>
+      <c r="B1091" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1091" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1091" t="s">
+        <v>148</v>
+      </c>
+      <c r="E1091" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1091" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1091" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1091" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1091" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1091" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1091" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1091" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1091" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1091" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1091" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1091" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1092" t="s">
+        <v>5283</v>
+      </c>
+      <c r="B1092" t="s">
+        <v>3661</v>
+      </c>
+      <c r="C1092" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1092" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1092" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1092" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1092" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1092" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1092" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1092" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1092" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1092" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1092" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1092" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1092" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1092" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -69195,7 +71527,7 @@
         <v>2</v>
       </c>
       <c r="C1" s="32" t="s">
-        <v>5240</v>
+        <v>5284</v>
       </c>
       <c r="D1" s="32" t="s">
         <v>53</v>
@@ -69228,7 +71560,7 @@
         <v>9</v>
       </c>
       <c r="N1" s="32" t="s">
-        <v>5241</v>
+        <v>5285</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -69272,7 +71604,7 @@
         <v>39</v>
       </c>
       <c r="N2" s="34" t="s">
-        <v>5242</v>
+        <v>5286</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -69316,7 +71648,7 @@
         <v>36</v>
       </c>
       <c r="N3" s="36" t="s">
-        <v>5242</v>
+        <v>5286</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -69360,7 +71692,7 @@
         <v>35</v>
       </c>
       <c r="N4" s="34" t="s">
-        <v>5242</v>
+        <v>5286</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -69404,7 +71736,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="36" t="s">
-        <v>5243</v>
+        <v>5287</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -69448,7 +71780,7 @@
         <v>33</v>
       </c>
       <c r="N6" s="34" t="s">
-        <v>5242</v>
+        <v>5286</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -69492,7 +71824,7 @@
         <v>22</v>
       </c>
       <c r="N7" s="36" t="s">
-        <v>5242</v>
+        <v>5286</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -69536,7 +71868,7 @@
         <v>36</v>
       </c>
       <c r="N8" s="34" t="s">
-        <v>5242</v>
+        <v>5286</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -69580,7 +71912,7 @@
         <v>34</v>
       </c>
       <c r="N9" s="36" t="s">
-        <v>5242</v>
+        <v>5286</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -69624,7 +71956,7 @@
         <v>36</v>
       </c>
       <c r="N10" s="34" t="s">
-        <v>5242</v>
+        <v>5286</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -69668,12 +72000,12 @@
         <v>29</v>
       </c>
       <c r="N11" s="36" t="s">
-        <v>5242</v>
+        <v>5286</v>
       </c>
     </row>
     <row r="13" spans="1:14" s="37" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="37" t="s">
-        <v>5244</v>
+        <v>5288</v>
       </c>
       <c r="B13" s="37" t="s">
         <v>30</v>
@@ -69685,7 +72017,7 @@
         <v>300</v>
       </c>
       <c r="N13" s="37" t="s">
-        <v>5245</v>
+        <v>5289</v>
       </c>
     </row>
   </sheetData>
@@ -69709,7 +72041,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="32" t="s">
-        <v>5246</v>
+        <v>5290</v>
       </c>
       <c r="C1" s="32" t="s">
         <v>9</v>
@@ -69816,7 +72148,7 @@
     </row>
     <row r="12" spans="1:3" s="37" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="37" t="s">
-        <v>5247</v>
+        <v>5291</v>
       </c>
       <c r="B12" s="37">
         <v>332</v>

--- a/manual-qa-repository/07-execution/TestCases-Consolidated.xlsx
+++ b/manual-qa-repository/07-execution/TestCases-Consolidated.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17382" uniqueCount="5292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17686" uniqueCount="5313">
   <si>
     <t>TC ID</t>
   </si>
@@ -16545,6 +16545,69 @@
   </si>
   <si>
     <t>TC_PHYSALLOC_UI_055</t>
+  </si>
+  <si>
+    <t>TC_BUYUD_NEG_001</t>
+  </si>
+  <si>
+    <t>FULL</t>
+  </si>
+  <si>
+    <t>TC_BUYUD_NEG_002</t>
+  </si>
+  <si>
+    <t>TC_BUYUD_FUNC_001</t>
+  </si>
+  <si>
+    <t>TC_BUYUD_FUNC_002</t>
+  </si>
+  <si>
+    <t>TC_BUYUD_FUNC_003</t>
+  </si>
+  <si>
+    <t>TC_BUYUD_VAL_001</t>
+  </si>
+  <si>
+    <t>TC_BUYUD_FUNC_004</t>
+  </si>
+  <si>
+    <t>TC_BUYUD_FUNC_005</t>
+  </si>
+  <si>
+    <t>TC_BUYUD_FUNC_006</t>
+  </si>
+  <si>
+    <t>TC_BUYUD_FUNC_007</t>
+  </si>
+  <si>
+    <t>TC_BUYUD_FUNC_008</t>
+  </si>
+  <si>
+    <t>TC_BUYUD_BIZ_001</t>
+  </si>
+  <si>
+    <t>TC_BUYUD_NEG_003</t>
+  </si>
+  <si>
+    <t>FULL (negative)</t>
+  </si>
+  <si>
+    <t>TC_BUYUD_NEG_004</t>
+  </si>
+  <si>
+    <t>TC_BUYUD_UI_001</t>
+  </si>
+  <si>
+    <t>TC_BUYUD_UI_002</t>
+  </si>
+  <si>
+    <t>TC_BUYUD_REG_001</t>
+  </si>
+  <si>
+    <t>TC_BUYUD_XMOD_001</t>
+  </si>
+  <si>
+    <t>TC_BUYUD_EDGE_001</t>
   </si>
   <si>
     <t>Total TCs</t>
@@ -17167,7 +17230,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P1092"/>
+  <dimension ref="A1:P1111"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -71485,6 +71548,956 @@
       </c>
       <c r="P1092" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1093" t="s">
+        <v>5284</v>
+      </c>
+      <c r="B1093" t="s">
+        <v>1650</v>
+      </c>
+      <c r="C1093" t="s">
+        <v>2670</v>
+      </c>
+      <c r="D1093" t="s">
+        <v>148</v>
+      </c>
+      <c r="E1093" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1093" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1093" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1093" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1093" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1093" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1093" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1093" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1093" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1093" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1093" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1093" t="s">
+        <v>5285</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1094" t="s">
+        <v>5286</v>
+      </c>
+      <c r="B1094" t="s">
+        <v>1650</v>
+      </c>
+      <c r="C1094" t="s">
+        <v>2670</v>
+      </c>
+      <c r="D1094" t="s">
+        <v>148</v>
+      </c>
+      <c r="E1094" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1094" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1094" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1094" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1094" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1094" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1094" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1094" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1094" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1094" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1094" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1094" t="s">
+        <v>5285</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1095" t="s">
+        <v>5287</v>
+      </c>
+      <c r="B1095" t="s">
+        <v>1650</v>
+      </c>
+      <c r="C1095" t="s">
+        <v>2670</v>
+      </c>
+      <c r="D1095" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1095" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1095" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1095" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1095" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1095" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1095" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1095" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1095" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1095" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1095" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1095" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1095" t="s">
+        <v>5285</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1096" t="s">
+        <v>5288</v>
+      </c>
+      <c r="B1096" t="s">
+        <v>1650</v>
+      </c>
+      <c r="C1096" t="s">
+        <v>2670</v>
+      </c>
+      <c r="D1096" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1096" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1096" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1096" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1096" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1096" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1096" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1096" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1096" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1096" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1096" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1096" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1096" t="s">
+        <v>5285</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1097" t="s">
+        <v>5289</v>
+      </c>
+      <c r="B1097" t="s">
+        <v>1650</v>
+      </c>
+      <c r="C1097" t="s">
+        <v>2670</v>
+      </c>
+      <c r="D1097" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1097" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1097" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1097" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1097" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1097" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1097" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1097" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1097" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1097" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1097" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1097" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1097" t="s">
+        <v>5285</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1098" t="s">
+        <v>5290</v>
+      </c>
+      <c r="B1098" t="s">
+        <v>1650</v>
+      </c>
+      <c r="C1098" t="s">
+        <v>2670</v>
+      </c>
+      <c r="D1098" t="s">
+        <v>119</v>
+      </c>
+      <c r="E1098" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1098" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1098" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1098" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1098" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1098" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1098" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1098" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1098" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1098" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1098" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1098" t="s">
+        <v>5285</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1099" t="s">
+        <v>5291</v>
+      </c>
+      <c r="B1099" t="s">
+        <v>1650</v>
+      </c>
+      <c r="C1099" t="s">
+        <v>2670</v>
+      </c>
+      <c r="D1099" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1099" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1099" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1099" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1099" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1099" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1099" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1099" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1099" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1099" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1099" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1099" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1099" t="s">
+        <v>5285</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1100" t="s">
+        <v>5292</v>
+      </c>
+      <c r="B1100" t="s">
+        <v>1650</v>
+      </c>
+      <c r="C1100" t="s">
+        <v>2670</v>
+      </c>
+      <c r="D1100" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1100" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1100" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1100" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1100" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1100" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1100" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1100" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1100" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1100" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1100" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1100" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1100" t="s">
+        <v>5285</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1101" t="s">
+        <v>5293</v>
+      </c>
+      <c r="B1101" t="s">
+        <v>1650</v>
+      </c>
+      <c r="C1101" t="s">
+        <v>2670</v>
+      </c>
+      <c r="D1101" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1101" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1101" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1101" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1101" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1101" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1101" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1101" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1101" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1101" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1101" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1101" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1101" t="s">
+        <v>5285</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1102" t="s">
+        <v>5294</v>
+      </c>
+      <c r="B1102" t="s">
+        <v>1650</v>
+      </c>
+      <c r="C1102" t="s">
+        <v>2670</v>
+      </c>
+      <c r="D1102" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1102" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1102" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1102" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1102" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1102" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1102" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1102" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1102" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1102" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1102" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1102" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1102" t="s">
+        <v>5285</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1103" t="s">
+        <v>5295</v>
+      </c>
+      <c r="B1103" t="s">
+        <v>1650</v>
+      </c>
+      <c r="C1103" t="s">
+        <v>2670</v>
+      </c>
+      <c r="D1103" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1103" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1103" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1103" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1103" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1103" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1103" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1103" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1103" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1103" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1103" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1103" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1103" t="s">
+        <v>5285</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1104" t="s">
+        <v>5296</v>
+      </c>
+      <c r="B1104" t="s">
+        <v>1650</v>
+      </c>
+      <c r="C1104" t="s">
+        <v>2670</v>
+      </c>
+      <c r="D1104" t="s">
+        <v>186</v>
+      </c>
+      <c r="E1104" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1104" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1104" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1104" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1104" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1104" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1104" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1104" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1104" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1104" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1104" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1104" t="s">
+        <v>5285</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1105" t="s">
+        <v>5297</v>
+      </c>
+      <c r="B1105" t="s">
+        <v>1650</v>
+      </c>
+      <c r="C1105" t="s">
+        <v>2670</v>
+      </c>
+      <c r="D1105" t="s">
+        <v>148</v>
+      </c>
+      <c r="E1105" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1105" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1105" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1105" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1105" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1105" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1105" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1105" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1105" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1105" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1105" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1105" t="s">
+        <v>5298</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1106" t="s">
+        <v>5299</v>
+      </c>
+      <c r="B1106" t="s">
+        <v>1650</v>
+      </c>
+      <c r="C1106" t="s">
+        <v>2670</v>
+      </c>
+      <c r="D1106" t="s">
+        <v>148</v>
+      </c>
+      <c r="E1106" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1106" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1106" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1106" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1106" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1106" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1106" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1106" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1106" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1106" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1106" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1106" t="s">
+        <v>5298</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1107" t="s">
+        <v>5300</v>
+      </c>
+      <c r="B1107" t="s">
+        <v>1650</v>
+      </c>
+      <c r="C1107" t="s">
+        <v>2670</v>
+      </c>
+      <c r="D1107" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1107" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1107" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1107" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1107" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1107" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1107" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1107" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1107" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1107" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1107" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1107" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1107" t="s">
+        <v>5285</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1108" t="s">
+        <v>5301</v>
+      </c>
+      <c r="B1108" t="s">
+        <v>1650</v>
+      </c>
+      <c r="C1108" t="s">
+        <v>2670</v>
+      </c>
+      <c r="D1108" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1108" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1108" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1108" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1108" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1108" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1108" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1108" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1108" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1108" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1108" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1108" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1108" t="s">
+        <v>5285</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1109" t="s">
+        <v>5302</v>
+      </c>
+      <c r="B1109" t="s">
+        <v>1650</v>
+      </c>
+      <c r="C1109" t="s">
+        <v>2670</v>
+      </c>
+      <c r="D1109" t="s">
+        <v>749</v>
+      </c>
+      <c r="E1109" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1109" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1109" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1109" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1109" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1109" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1109" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1109" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1109" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1109" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1109" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1109" t="s">
+        <v>5285</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1110" t="s">
+        <v>5303</v>
+      </c>
+      <c r="B1110" t="s">
+        <v>1650</v>
+      </c>
+      <c r="C1110" t="s">
+        <v>2670</v>
+      </c>
+      <c r="D1110" t="s">
+        <v>2688</v>
+      </c>
+      <c r="E1110" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1110" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1110" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1110" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1110" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1110" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1110" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1110" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1110" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1110" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1110" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1110" t="s">
+        <v>5285</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1111" t="s">
+        <v>5304</v>
+      </c>
+      <c r="B1111" t="s">
+        <v>1650</v>
+      </c>
+      <c r="C1111" t="s">
+        <v>2670</v>
+      </c>
+      <c r="D1111" t="s">
+        <v>170</v>
+      </c>
+      <c r="E1111" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1111" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1111" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1111" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1111" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1111" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1111" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1111" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1111" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N1111" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1111" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1111" t="s">
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -71527,7 +72540,7 @@
         <v>2</v>
       </c>
       <c r="C1" s="32" t="s">
-        <v>5284</v>
+        <v>5305</v>
       </c>
       <c r="D1" s="32" t="s">
         <v>53</v>
@@ -71560,7 +72573,7 @@
         <v>9</v>
       </c>
       <c r="N1" s="32" t="s">
-        <v>5285</v>
+        <v>5306</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -71604,7 +72617,7 @@
         <v>39</v>
       </c>
       <c r="N2" s="34" t="s">
-        <v>5286</v>
+        <v>5307</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -71648,7 +72661,7 @@
         <v>36</v>
       </c>
       <c r="N3" s="36" t="s">
-        <v>5286</v>
+        <v>5307</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -71692,7 +72705,7 @@
         <v>35</v>
       </c>
       <c r="N4" s="34" t="s">
-        <v>5286</v>
+        <v>5307</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -71736,7 +72749,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="36" t="s">
-        <v>5287</v>
+        <v>5308</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -71780,7 +72793,7 @@
         <v>33</v>
       </c>
       <c r="N6" s="34" t="s">
-        <v>5286</v>
+        <v>5307</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -71824,7 +72837,7 @@
         <v>22</v>
       </c>
       <c r="N7" s="36" t="s">
-        <v>5286</v>
+        <v>5307</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -71868,7 +72881,7 @@
         <v>36</v>
       </c>
       <c r="N8" s="34" t="s">
-        <v>5286</v>
+        <v>5307</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -71912,7 +72925,7 @@
         <v>34</v>
       </c>
       <c r="N9" s="36" t="s">
-        <v>5286</v>
+        <v>5307</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -71956,7 +72969,7 @@
         <v>36</v>
       </c>
       <c r="N10" s="34" t="s">
-        <v>5286</v>
+        <v>5307</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -72000,12 +73013,12 @@
         <v>29</v>
       </c>
       <c r="N11" s="36" t="s">
-        <v>5286</v>
+        <v>5307</v>
       </c>
     </row>
     <row r="13" spans="1:14" s="37" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="37" t="s">
-        <v>5288</v>
+        <v>5309</v>
       </c>
       <c r="B13" s="37" t="s">
         <v>30</v>
@@ -72017,7 +73030,7 @@
         <v>300</v>
       </c>
       <c r="N13" s="37" t="s">
-        <v>5289</v>
+        <v>5310</v>
       </c>
     </row>
   </sheetData>
@@ -72041,7 +73054,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="32" t="s">
-        <v>5290</v>
+        <v>5311</v>
       </c>
       <c r="C1" s="32" t="s">
         <v>9</v>
@@ -72148,7 +73161,7 @@
     </row>
     <row r="12" spans="1:3" s="37" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="37" t="s">
-        <v>5291</v>
+        <v>5312</v>
       </c>
       <c r="B12" s="37">
         <v>332</v>
